--- a/MomijiStore_OS/02_Analytics/SourceData/楽天運営 KPI管理シート.xlsx
+++ b/MomijiStore_OS/02_Analytics/SourceData/楽天運営 KPI管理シート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hide0726/Desktop/Claude Code/MomijiStore_OS/02_Analytics/SourceData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8AA58916F7DB843E46CDF2A37470C61743A3DE77" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_92CD296F0687250FB87CF8C0F4C503A5F002C1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6697,7 +6697,7 @@
     <numFmt numFmtId="176" formatCode="0.0%"/>
     <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -6801,6 +6801,14 @@
       <sz val="6"/>
       <name val="Arial"/>
       <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -7017,12 +7025,12 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -64940,7 +64948,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="45" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" style="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -64992,7 +65000,7 @@
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -65036,7 +65044,7 @@
       <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>26</v>
       </c>
       <c r="E8" t="s">
@@ -65081,7 +65089,7 @@
       <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="46" t="s">
+      <c r="D9" s="45" t="s">
         <v>29</v>
       </c>
       <c r="E9" t="s">
@@ -65126,7 +65134,7 @@
       <c r="C10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="46" t="s">
+      <c r="D10" s="45" t="s">
         <v>33</v>
       </c>
       <c r="E10" t="s">
@@ -65171,7 +65179,7 @@
       <c r="C11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="46">
+      <c r="D11" s="45">
         <v>4902430898706</v>
       </c>
       <c r="E11" t="s">
@@ -65216,7 +65224,7 @@
       <c r="C12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="45" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
@@ -65262,7 +65270,7 @@
       <c r="C13" s="1">
         <v>4550391012121</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="1">
@@ -65307,7 +65315,7 @@
       <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="45" t="s">
         <v>44</v>
       </c>
       <c r="E14" t="s">
@@ -65352,7 +65360,7 @@
       <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>48</v>
       </c>
       <c r="E15" t="s">
@@ -65397,7 +65405,7 @@
       <c r="C16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="45">
         <v>36300</v>
       </c>
       <c r="E16" t="s">
@@ -65445,7 +65453,7 @@
       <c r="C17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="46" t="s">
+      <c r="D17" s="45" t="s">
         <v>54</v>
       </c>
       <c r="E17" t="s">
@@ -65490,7 +65498,7 @@
       <c r="C18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="46" t="s">
+      <c r="D18" s="45" t="s">
         <v>58</v>
       </c>
       <c r="E18" t="s">
@@ -65535,7 +65543,7 @@
       <c r="C19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="46" t="s">
+      <c r="D19" s="45" t="s">
         <v>61</v>
       </c>
       <c r="E19" t="s">
@@ -65580,7 +65588,7 @@
       <c r="C20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="45" t="s">
         <v>64</v>
       </c>
       <c r="E20" t="s">
@@ -65625,7 +65633,7 @@
       <c r="C21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="45" t="s">
         <v>67</v>
       </c>
       <c r="E21" t="s">
@@ -65670,7 +65678,7 @@
       <c r="C22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="46" t="s">
+      <c r="D22" s="45" t="s">
         <v>70</v>
       </c>
       <c r="E22" t="s">
@@ -65715,7 +65723,7 @@
       <c r="C23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="45" t="s">
         <v>74</v>
       </c>
       <c r="E23" t="s">
@@ -65760,7 +65768,7 @@
       <c r="C24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="45" t="s">
         <v>77</v>
       </c>
       <c r="E24" t="s">
@@ -65808,7 +65816,7 @@
       <c r="C25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="45" t="s">
         <v>80</v>
       </c>
       <c r="E25" t="s">
@@ -65853,7 +65861,7 @@
       <c r="C26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="46">
+      <c r="D26" s="45">
         <v>9524</v>
       </c>
       <c r="E26" t="s">
@@ -65898,7 +65906,7 @@
       <c r="C27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="45" t="s">
         <v>86</v>
       </c>
       <c r="E27" t="s">
@@ -65943,7 +65951,7 @@
       <c r="C28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="45" t="s">
         <v>89</v>
       </c>
       <c r="E28" t="s">
@@ -65991,7 +65999,7 @@
       <c r="C29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="45" t="s">
         <v>92</v>
       </c>
       <c r="E29" t="s">
@@ -66037,7 +66045,7 @@
       <c r="C30" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D30" s="45" t="s">
         <v>96</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -66082,7 +66090,7 @@
       <c r="C31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="46">
+      <c r="D31" s="45">
         <v>840414639447</v>
       </c>
       <c r="E31" t="s">
@@ -66127,7 +66135,7 @@
       <c r="C32" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="45" t="s">
         <v>102</v>
       </c>
       <c r="E32" t="s">
@@ -66172,7 +66180,7 @@
       <c r="C33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="45" t="s">
         <v>105</v>
       </c>
       <c r="E33" t="s">
@@ -66217,7 +66225,7 @@
       <c r="C34" s="1">
         <v>4550391042821</v>
       </c>
-      <c r="D34" s="46" t="s">
+      <c r="D34" s="45" t="s">
         <v>107</v>
       </c>
       <c r="E34">
@@ -66263,7 +66271,7 @@
       <c r="C35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="46" t="s">
+      <c r="D35" s="45" t="s">
         <v>110</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -66309,7 +66317,7 @@
       <c r="C36" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="46">
+      <c r="D36" s="45">
         <v>2486</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -66355,7 +66363,7 @@
       <c r="C37" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="46" t="s">
+      <c r="D37" s="45" t="s">
         <v>116</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -66401,7 +66409,7 @@
       <c r="C38" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="46" t="s">
+      <c r="D38" s="45" t="s">
         <v>119</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -66446,7 +66454,7 @@
       <c r="C39" s="1">
         <v>3264680024993</v>
       </c>
-      <c r="D39" s="46" t="s">
+      <c r="D39" s="45" t="s">
         <v>121</v>
       </c>
       <c r="E39">
@@ -66491,7 +66499,7 @@
       <c r="C40" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="46" t="s">
+      <c r="D40" s="45" t="s">
         <v>124</v>
       </c>
       <c r="E40" t="s">
@@ -66539,7 +66547,7 @@
       <c r="C41" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="46" t="s">
+      <c r="D41" s="45" t="s">
         <v>54</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -66587,7 +66595,7 @@
       <c r="C42" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D42" s="46" t="s">
+      <c r="D42" s="45" t="s">
         <v>130</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -66632,7 +66640,7 @@
       <c r="C43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D43" s="46" t="s">
+      <c r="D43" s="45" t="s">
         <v>134</v>
       </c>
       <c r="E43" t="s">
@@ -66677,7 +66685,7 @@
       <c r="C44" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="46" t="s">
+      <c r="D44" s="45" t="s">
         <v>137</v>
       </c>
       <c r="E44" t="s">
@@ -66722,7 +66730,7 @@
       <c r="C45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="46" t="s">
+      <c r="D45" s="45" t="s">
         <v>140</v>
       </c>
       <c r="E45" t="s">
@@ -66767,7 +66775,7 @@
       <c r="C46" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D46" s="46" t="s">
+      <c r="D46" s="45" t="s">
         <v>143</v>
       </c>
       <c r="E46" t="s">
@@ -66812,7 +66820,7 @@
       <c r="C47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="46" t="s">
+      <c r="D47" s="45" t="s">
         <v>146</v>
       </c>
       <c r="E47" t="s">
@@ -66857,7 +66865,7 @@
       <c r="C48" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D48" s="46" t="s">
+      <c r="D48" s="45" t="s">
         <v>149</v>
       </c>
       <c r="E48" t="s">
@@ -66905,7 +66913,7 @@
       <c r="C49" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="46" t="s">
+      <c r="D49" s="45" t="s">
         <v>153</v>
       </c>
       <c r="E49" t="s">
@@ -66953,7 +66961,7 @@
       <c r="C50" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="46" t="s">
+      <c r="D50" s="45" t="s">
         <v>153</v>
       </c>
       <c r="E50" t="s">
@@ -66998,7 +67006,7 @@
       <c r="C51" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D51" s="46" t="s">
+      <c r="D51" s="45" t="s">
         <v>159</v>
       </c>
       <c r="E51" t="s">
@@ -67043,7 +67051,7 @@
       <c r="C52" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="46" t="s">
+      <c r="D52" s="45" t="s">
         <v>163</v>
       </c>
       <c r="E52" t="s">
@@ -67089,7 +67097,7 @@
       <c r="C53" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D53" s="46" t="s">
+      <c r="D53" s="45" t="s">
         <v>166</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -67137,7 +67145,7 @@
       <c r="C54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D54" s="46" t="s">
+      <c r="D54" s="45" t="s">
         <v>170</v>
       </c>
       <c r="E54" t="s">
@@ -67182,7 +67190,7 @@
       <c r="C55" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D55" s="46" t="s">
+      <c r="D55" s="45" t="s">
         <v>174</v>
       </c>
       <c r="E55" t="s">
@@ -67228,7 +67236,7 @@
       <c r="C56" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D56" s="46" t="s">
+      <c r="D56" s="45" t="s">
         <v>177</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -67273,7 +67281,7 @@
       <c r="C57" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D57" s="46" t="s">
+      <c r="D57" s="45" t="s">
         <v>180</v>
       </c>
       <c r="E57" t="s">
@@ -67318,7 +67326,7 @@
       <c r="C58" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D58" s="46" t="s">
+      <c r="D58" s="45" t="s">
         <v>183</v>
       </c>
       <c r="E58" t="s">
@@ -67364,7 +67372,7 @@
       <c r="C59" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="46" t="s">
+      <c r="D59" s="45" t="s">
         <v>187</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -67409,7 +67417,7 @@
       <c r="C60" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="46" t="s">
+      <c r="D60" s="45" t="s">
         <v>191</v>
       </c>
       <c r="E60" t="s">
@@ -67455,7 +67463,7 @@
       <c r="C61" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D61" s="46" t="s">
+      <c r="D61" s="45" t="s">
         <v>194</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -67500,7 +67508,7 @@
       <c r="C62" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D62" s="46" t="s">
+      <c r="D62" s="45" t="s">
         <v>198</v>
       </c>
       <c r="E62" t="s">
@@ -67548,7 +67556,7 @@
       <c r="C63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="46" t="s">
+      <c r="D63" s="45" t="s">
         <v>202</v>
       </c>
       <c r="E63" t="s">
@@ -67593,7 +67601,7 @@
       <c r="C64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="46" t="s">
+      <c r="D64" s="45" t="s">
         <v>206</v>
       </c>
       <c r="E64" t="s">
@@ -67638,7 +67646,7 @@
       <c r="C65" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="46" t="s">
+      <c r="D65" s="45" t="s">
         <v>209</v>
       </c>
       <c r="E65" t="s">
@@ -67683,7 +67691,7 @@
       <c r="C66" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="46" t="s">
+      <c r="D66" s="45" t="s">
         <v>212</v>
       </c>
       <c r="E66" t="s">
@@ -67728,7 +67736,7 @@
       <c r="C67" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="46" t="s">
+      <c r="D67" s="45" t="s">
         <v>215</v>
       </c>
       <c r="E67" t="s">
@@ -67773,7 +67781,7 @@
       <c r="C68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="46" t="s">
+      <c r="D68" s="45" t="s">
         <v>218</v>
       </c>
       <c r="E68" t="s">
@@ -67821,7 +67829,7 @@
       <c r="C69" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="46" t="s">
+      <c r="D69" s="45" t="s">
         <v>221</v>
       </c>
       <c r="E69" t="s">
@@ -67866,7 +67874,7 @@
       <c r="C70" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D70" s="46" t="s">
+      <c r="D70" s="45" t="s">
         <v>225</v>
       </c>
       <c r="E70" t="s">
@@ -67911,7 +67919,7 @@
       <c r="C71" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D71" s="46" t="s">
+      <c r="D71" s="45" t="s">
         <v>228</v>
       </c>
       <c r="E71" t="s">
@@ -67956,7 +67964,7 @@
       <c r="C72" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D72" s="46" t="s">
+      <c r="D72" s="45" t="s">
         <v>231</v>
       </c>
       <c r="E72" t="s">
@@ -68001,7 +68009,7 @@
       <c r="C73" s="1">
         <v>4550391911226</v>
       </c>
-      <c r="D73" s="46" t="s">
+      <c r="D73" s="45" t="s">
         <v>234</v>
       </c>
       <c r="E73">
@@ -68046,7 +68054,7 @@
       <c r="C74" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D74" s="46" t="s">
+      <c r="D74" s="45" t="s">
         <v>237</v>
       </c>
       <c r="E74" t="s">
@@ -68091,7 +68099,7 @@
       <c r="C75" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D75" s="46" t="s">
+      <c r="D75" s="45" t="s">
         <v>240</v>
       </c>
       <c r="E75" t="s">
@@ -68136,7 +68144,7 @@
       <c r="C76" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D76" s="46" t="s">
+      <c r="D76" s="45" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
@@ -68181,7 +68189,7 @@
       <c r="C77" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D77" s="46" t="s">
+      <c r="D77" s="45" t="s">
         <v>246</v>
       </c>
       <c r="E77" t="s">
@@ -68226,7 +68234,7 @@
       <c r="C78" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D78" s="46" t="s">
+      <c r="D78" s="45" t="s">
         <v>249</v>
       </c>
       <c r="E78" t="s">
@@ -68271,7 +68279,7 @@
       <c r="C79" s="1">
         <v>4550391910564</v>
       </c>
-      <c r="D79" s="46" t="s">
+      <c r="D79" s="45" t="s">
         <v>252</v>
       </c>
       <c r="E79">
@@ -68316,7 +68324,7 @@
       <c r="C80" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D80" s="46" t="s">
+      <c r="D80" s="45" t="s">
         <v>255</v>
       </c>
       <c r="E80" t="s">
@@ -68361,7 +68369,7 @@
       <c r="C81" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D81" s="46">
+      <c r="D81" s="45">
         <v>4571263111773</v>
       </c>
       <c r="E81" t="s">
@@ -68407,7 +68415,7 @@
       <c r="C82" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D82" s="46" t="s">
+      <c r="D82" s="45" t="s">
         <v>260</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -68452,7 +68460,7 @@
       <c r="C83" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D83" s="46" t="s">
+      <c r="D83" s="45" t="s">
         <v>263</v>
       </c>
       <c r="E83" t="s">
@@ -68497,7 +68505,7 @@
       <c r="C84" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D84" s="46">
+      <c r="D84" s="45">
         <v>4901133718984</v>
       </c>
       <c r="E84" t="s">
@@ -68545,7 +68553,7 @@
       <c r="C85" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D85" s="46" t="s">
+      <c r="D85" s="45" t="s">
         <v>270</v>
       </c>
       <c r="E85" t="s">
@@ -68593,7 +68601,7 @@
       <c r="C86" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D86" s="46">
+      <c r="D86" s="45">
         <v>7480</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -68638,7 +68646,7 @@
       <c r="C87" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D87" s="46" t="s">
+      <c r="D87" s="45" t="s">
         <v>278</v>
       </c>
       <c r="E87" t="s">
@@ -68683,7 +68691,7 @@
       <c r="C88" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D88" s="46" t="s">
+      <c r="D88" s="45" t="s">
         <v>281</v>
       </c>
       <c r="E88" t="s">
@@ -68728,7 +68736,7 @@
       <c r="C89" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D89" s="46" t="s">
+      <c r="D89" s="45" t="s">
         <v>284</v>
       </c>
       <c r="E89" t="s">
@@ -68776,7 +68784,7 @@
       <c r="C90" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D90" s="46">
+      <c r="D90" s="45">
         <v>194644137595</v>
       </c>
       <c r="E90" t="s">
@@ -68824,7 +68832,7 @@
       <c r="C91" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D91" s="46" t="s">
+      <c r="D91" s="45" t="s">
         <v>291</v>
       </c>
       <c r="E91" t="s">
@@ -68869,7 +68877,7 @@
       <c r="C92" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D92" s="46" t="s">
+      <c r="D92" s="45" t="s">
         <v>295</v>
       </c>
       <c r="E92" t="s">
@@ -68914,7 +68922,7 @@
       <c r="C93" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D93" s="46" t="s">
+      <c r="D93" s="45" t="s">
         <v>298</v>
       </c>
       <c r="E93" t="s">
@@ -68959,7 +68967,7 @@
       <c r="C94" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D94" s="46" t="s">
+      <c r="D94" s="45" t="s">
         <v>301</v>
       </c>
       <c r="E94" t="s">
@@ -69004,7 +69012,7 @@
       <c r="C95" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D95" s="46" t="s">
+      <c r="D95" s="45" t="s">
         <v>305</v>
       </c>
       <c r="E95" t="s">
@@ -69050,7 +69058,7 @@
       <c r="C96" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D96" s="46" t="s">
+      <c r="D96" s="45" t="s">
         <v>308</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -69095,7 +69103,7 @@
       <c r="C97" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D97" s="46" t="s">
+      <c r="D97" s="45" t="s">
         <v>311</v>
       </c>
       <c r="E97" t="s">
@@ -69143,7 +69151,7 @@
       <c r="C98" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D98" s="46" t="s">
+      <c r="D98" s="45" t="s">
         <v>54</v>
       </c>
       <c r="E98" t="s">
@@ -69189,7 +69197,7 @@
       <c r="C99" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D99" s="46" t="s">
+      <c r="D99" s="45" t="s">
         <v>316</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -69234,7 +69242,7 @@
       <c r="C100" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D100" s="46" t="s">
+      <c r="D100" s="45" t="s">
         <v>320</v>
       </c>
       <c r="E100" t="s">
@@ -69279,7 +69287,7 @@
       <c r="C101" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D101" s="46">
+      <c r="D101" s="45">
         <v>840414684973</v>
       </c>
       <c r="E101" t="s">
@@ -69324,7 +69332,7 @@
       <c r="C102" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D102" s="46" t="s">
+      <c r="D102" s="45" t="s">
         <v>326</v>
       </c>
       <c r="E102" t="s">
@@ -69372,7 +69380,7 @@
       <c r="C103" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D103" s="46" t="s">
+      <c r="D103" s="45" t="s">
         <v>329</v>
       </c>
       <c r="E103" t="s">
@@ -69417,7 +69425,7 @@
       <c r="C104" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D104" s="46" t="s">
+      <c r="D104" s="45" t="s">
         <v>170</v>
       </c>
       <c r="E104" t="s">
@@ -69465,7 +69473,7 @@
       <c r="C105" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D105" s="46" t="s">
+      <c r="D105" s="45" t="s">
         <v>170</v>
       </c>
       <c r="E105" t="s">
@@ -69510,7 +69518,7 @@
       <c r="C106" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D106" s="46" t="s">
+      <c r="D106" s="45" t="s">
         <v>334</v>
       </c>
       <c r="E106" t="s">
@@ -69555,7 +69563,7 @@
       <c r="C107" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D107" s="46" t="s">
+      <c r="D107" s="45" t="s">
         <v>337</v>
       </c>
       <c r="E107" t="s">
@@ -69601,7 +69609,7 @@
       <c r="C108" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D108" s="46" t="s">
+      <c r="D108" s="45" t="s">
         <v>340</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -69646,7 +69654,7 @@
       <c r="C109" s="1">
         <v>4550391046515</v>
       </c>
-      <c r="D109" s="46" t="s">
+      <c r="D109" s="45" t="s">
         <v>342</v>
       </c>
       <c r="E109">
@@ -69691,7 +69699,7 @@
       <c r="C110" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D110" s="46" t="s">
+      <c r="D110" s="45" t="s">
         <v>345</v>
       </c>
       <c r="E110" t="s">
@@ -69736,7 +69744,7 @@
       <c r="C111" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D111" s="46" t="s">
+      <c r="D111" s="45" t="s">
         <v>348</v>
       </c>
       <c r="E111" t="s">
@@ -69782,7 +69790,7 @@
       <c r="C112" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D112" s="46" t="s">
+      <c r="D112" s="45" t="s">
         <v>352</v>
       </c>
       <c r="E112" s="1" t="s">
@@ -69827,7 +69835,7 @@
       <c r="C113" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D113" s="46" t="s">
+      <c r="D113" s="45" t="s">
         <v>356</v>
       </c>
       <c r="E113" t="s">
@@ -69872,7 +69880,7 @@
       <c r="C114" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D114" s="46" t="s">
+      <c r="D114" s="45" t="s">
         <v>359</v>
       </c>
       <c r="E114" t="s">
@@ -69917,7 +69925,7 @@
       <c r="C115" s="1">
         <v>8720689024570</v>
       </c>
-      <c r="D115" s="46" t="s">
+      <c r="D115" s="45" t="s">
         <v>361</v>
       </c>
       <c r="E115">
@@ -69965,7 +69973,7 @@
       <c r="C116" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D116" s="46" t="s">
+      <c r="D116" s="45" t="s">
         <v>364</v>
       </c>
       <c r="E116" t="s">
@@ -70010,7 +70018,7 @@
       <c r="C117" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D117" s="46" t="s">
+      <c r="D117" s="45" t="s">
         <v>368</v>
       </c>
       <c r="E117" t="s">
@@ -70055,7 +70063,7 @@
       <c r="C118" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D118" s="46" t="s">
+      <c r="D118" s="45" t="s">
         <v>371</v>
       </c>
       <c r="E118" t="s">
@@ -70100,7 +70108,7 @@
       <c r="C119" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D119" s="46" t="s">
+      <c r="D119" s="45" t="s">
         <v>374</v>
       </c>
       <c r="E119" t="s">
@@ -70145,7 +70153,7 @@
       <c r="C120" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D120" s="46" t="s">
+      <c r="D120" s="45" t="s">
         <v>377</v>
       </c>
       <c r="E120" t="s">
@@ -70191,7 +70199,7 @@
       <c r="C121" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D121" s="46" t="s">
+      <c r="D121" s="45" t="s">
         <v>381</v>
       </c>
       <c r="E121" s="1" t="s">
@@ -70236,7 +70244,7 @@
       <c r="C122" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D122" s="46" t="s">
+      <c r="D122" s="45" t="s">
         <v>385</v>
       </c>
       <c r="E122" t="s">
@@ -70282,7 +70290,7 @@
       <c r="C123" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D123" s="46" t="s">
+      <c r="D123" s="45" t="s">
         <v>389</v>
       </c>
       <c r="E123" s="1" t="s">
@@ -70327,7 +70335,7 @@
       <c r="C124" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D124" s="46" t="s">
+      <c r="D124" s="45" t="s">
         <v>393</v>
       </c>
       <c r="E124" t="s">
@@ -70375,7 +70383,7 @@
       <c r="C125" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D125" s="46" t="s">
+      <c r="D125" s="45" t="s">
         <v>396</v>
       </c>
       <c r="E125" t="s">
@@ -70423,7 +70431,7 @@
       <c r="C126" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D126" s="46" t="s">
+      <c r="D126" s="45" t="s">
         <v>202</v>
       </c>
       <c r="E126" t="s">
@@ -70471,7 +70479,7 @@
       <c r="C127" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D127" s="46">
+      <c r="D127" s="45">
         <v>4980</v>
       </c>
       <c r="E127" t="s">
@@ -70516,7 +70524,7 @@
       <c r="C128" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D128" s="45" t="s">
+      <c r="D128" s="44" t="s">
         <v>405</v>
       </c>
       <c r="E128" t="s">
@@ -70564,7 +70572,7 @@
       <c r="C129" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D129" s="46" t="s">
+      <c r="D129" s="45" t="s">
         <v>409</v>
       </c>
       <c r="E129" s="1" t="s">
@@ -70609,7 +70617,7 @@
       <c r="C130" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D130" s="46" t="s">
+      <c r="D130" s="45" t="s">
         <v>413</v>
       </c>
       <c r="E130" t="s">
@@ -70654,7 +70662,7 @@
       <c r="C131" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D131" s="46" t="s">
+      <c r="D131" s="45" t="s">
         <v>416</v>
       </c>
       <c r="E131" t="s">
@@ -70702,7 +70710,7 @@
       <c r="C132" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D132" s="46" t="s">
+      <c r="D132" s="45" t="s">
         <v>420</v>
       </c>
       <c r="E132" t="s">
@@ -70747,7 +70755,7 @@
       <c r="C133" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D133" s="46" t="s">
+      <c r="D133" s="45" t="s">
         <v>424</v>
       </c>
       <c r="E133" t="s">
@@ -70792,7 +70800,7 @@
       <c r="C134" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D134" s="46" t="s">
+      <c r="D134" s="45" t="s">
         <v>427</v>
       </c>
       <c r="E134" t="s">
@@ -70837,7 +70845,7 @@
       <c r="C135" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D135" s="46" t="s">
+      <c r="D135" s="45" t="s">
         <v>430</v>
       </c>
       <c r="E135" t="s">
@@ -70882,7 +70890,7 @@
       <c r="C136" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D136" s="46" t="s">
+      <c r="D136" s="45" t="s">
         <v>433</v>
       </c>
       <c r="E136" t="s">
@@ -70928,7 +70936,7 @@
       <c r="C137" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D137" s="46" t="s">
+      <c r="D137" s="45" t="s">
         <v>436</v>
       </c>
       <c r="E137" s="1" t="s">
@@ -70973,7 +70981,7 @@
       <c r="C138" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D138" s="46" t="s">
+      <c r="D138" s="45" t="s">
         <v>439</v>
       </c>
       <c r="E138" t="s">
@@ -71018,7 +71026,7 @@
       <c r="C139" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D139" s="46" t="s">
+      <c r="D139" s="45" t="s">
         <v>442</v>
       </c>
       <c r="E139" t="s">
@@ -71064,7 +71072,7 @@
       <c r="C140" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D140" s="46" t="s">
+      <c r="D140" s="45" t="s">
         <v>446</v>
       </c>
       <c r="E140" s="1" t="s">
@@ -71110,7 +71118,7 @@
       <c r="C141" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D141" s="46" t="s">
+      <c r="D141" s="45" t="s">
         <v>449</v>
       </c>
       <c r="E141" s="1" t="s">
@@ -71155,7 +71163,7 @@
       <c r="C142" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D142" s="46" t="s">
+      <c r="D142" s="45" t="s">
         <v>453</v>
       </c>
       <c r="E142" t="s">
@@ -71203,7 +71211,7 @@
       <c r="C143" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D143" s="46">
+      <c r="D143" s="45">
         <v>4906456568056</v>
       </c>
       <c r="E143" t="s">
@@ -71248,7 +71256,7 @@
       <c r="C144" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D144" s="46" t="s">
+      <c r="D144" s="45" t="s">
         <v>460</v>
       </c>
       <c r="E144" t="s">
@@ -71293,7 +71301,7 @@
       <c r="C145" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="D145" s="46" t="s">
+      <c r="D145" s="45" t="s">
         <v>463</v>
       </c>
       <c r="E145" t="s">
@@ -71338,7 +71346,7 @@
       <c r="C146" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D146" s="46" t="s">
+      <c r="D146" s="45" t="s">
         <v>466</v>
       </c>
       <c r="E146" t="s">
@@ -71383,7 +71391,7 @@
       <c r="C147" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D147" s="46" t="s">
+      <c r="D147" s="45" t="s">
         <v>470</v>
       </c>
       <c r="E147" t="s">
@@ -71431,7 +71439,7 @@
       <c r="C148" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D148" s="46" t="s">
+      <c r="D148" s="45" t="s">
         <v>474</v>
       </c>
       <c r="E148" s="1" t="s">
@@ -71476,7 +71484,7 @@
       <c r="C149" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D149" s="46" t="s">
+      <c r="D149" s="45" t="s">
         <v>478</v>
       </c>
       <c r="E149" t="s">
@@ -71521,7 +71529,7 @@
       <c r="C150" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="D150" s="46" t="s">
+      <c r="D150" s="45" t="s">
         <v>481</v>
       </c>
       <c r="E150" t="s">
@@ -71566,7 +71574,7 @@
       <c r="C151" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="D151" s="46" t="s">
+      <c r="D151" s="45" t="s">
         <v>484</v>
       </c>
       <c r="E151" t="s">
@@ -71611,7 +71619,7 @@
       <c r="C152" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D152" s="46" t="s">
+      <c r="D152" s="45" t="s">
         <v>487</v>
       </c>
       <c r="E152" t="s">
@@ -71656,7 +71664,7 @@
       <c r="C153" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D153" s="46" t="s">
+      <c r="D153" s="45" t="s">
         <v>490</v>
       </c>
       <c r="E153" t="s">
@@ -71701,7 +71709,7 @@
       <c r="C154" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D154" s="46" t="s">
+      <c r="D154" s="45" t="s">
         <v>493</v>
       </c>
       <c r="E154" t="s">
@@ -71746,7 +71754,7 @@
       <c r="C155" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D155" s="46" t="s">
+      <c r="D155" s="45" t="s">
         <v>497</v>
       </c>
       <c r="E155" t="s">
@@ -71791,7 +71799,7 @@
       <c r="C156" s="1">
         <v>4901416183737</v>
       </c>
-      <c r="D156" s="46" t="s">
+      <c r="D156" s="45" t="s">
         <v>499</v>
       </c>
       <c r="E156">
@@ -71836,7 +71844,7 @@
       <c r="C157" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D157" s="46" t="s">
+      <c r="D157" s="45" t="s">
         <v>502</v>
       </c>
       <c r="E157" t="s">
@@ -71881,7 +71889,7 @@
       <c r="C158" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="D158" s="46" t="s">
+      <c r="D158" s="45" t="s">
         <v>505</v>
       </c>
       <c r="E158" t="s">
@@ -71926,7 +71934,7 @@
       <c r="C159" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D159" s="46" t="s">
+      <c r="D159" s="45" t="s">
         <v>509</v>
       </c>
       <c r="E159" t="s">
@@ -71974,7 +71982,7 @@
       <c r="C160" s="1">
         <v>4550391046508</v>
       </c>
-      <c r="D160" s="46" t="s">
+      <c r="D160" s="45" t="s">
         <v>512</v>
       </c>
       <c r="E160" t="s">
@@ -72022,7 +72030,7 @@
       <c r="C161" s="1">
         <v>4550391046508</v>
       </c>
-      <c r="D161" s="46" t="s">
+      <c r="D161" s="45" t="s">
         <v>512</v>
       </c>
       <c r="E161" t="s">
@@ -72070,7 +72078,7 @@
       <c r="C162" s="1">
         <v>4550391046508</v>
       </c>
-      <c r="D162" s="46" t="s">
+      <c r="D162" s="45" t="s">
         <v>512</v>
       </c>
       <c r="E162" t="s">
@@ -72116,7 +72124,7 @@
       <c r="C163" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D163" s="46" t="s">
+      <c r="D163" s="45" t="s">
         <v>520</v>
       </c>
       <c r="E163" s="1" t="s">
@@ -72162,7 +72170,7 @@
       <c r="C164" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="D164" s="46" t="s">
+      <c r="D164" s="45" t="s">
         <v>523</v>
       </c>
       <c r="E164" s="1" t="s">
@@ -72207,7 +72215,7 @@
       <c r="C165" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D165" s="46" t="s">
+      <c r="D165" s="45" t="s">
         <v>526</v>
       </c>
       <c r="E165" t="s">
@@ -72252,7 +72260,7 @@
       <c r="C166" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D166" s="46" t="s">
+      <c r="D166" s="45" t="s">
         <v>530</v>
       </c>
       <c r="E166" t="s">
@@ -72297,7 +72305,7 @@
       <c r="C167" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D167" s="46" t="s">
+      <c r="D167" s="45" t="s">
         <v>533</v>
       </c>
       <c r="E167" t="s">
@@ -72343,7 +72351,7 @@
       <c r="C168" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="D168" s="46" t="s">
+      <c r="D168" s="45" t="s">
         <v>536</v>
       </c>
       <c r="E168" s="1" t="s">
@@ -72388,7 +72396,7 @@
       <c r="C169" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D169" s="46" t="s">
+      <c r="D169" s="45" t="s">
         <v>540</v>
       </c>
       <c r="E169" t="s">
@@ -72433,7 +72441,7 @@
       <c r="C170" s="1">
         <v>4902806133806</v>
       </c>
-      <c r="D170" s="46" t="s">
+      <c r="D170" s="45" t="s">
         <v>542</v>
       </c>
       <c r="E170">
@@ -72481,7 +72489,7 @@
       <c r="C171" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D171" s="46" t="s">
+      <c r="D171" s="45" t="s">
         <v>546</v>
       </c>
       <c r="E171" t="s">
@@ -72526,7 +72534,7 @@
       <c r="C172" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D172" s="46" t="s">
+      <c r="D172" s="45" t="s">
         <v>550</v>
       </c>
       <c r="E172" t="s">
@@ -72571,7 +72579,7 @@
       <c r="C173" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="D173" s="46">
+      <c r="D173" s="45">
         <v>4987176305657</v>
       </c>
       <c r="E173" t="s">
@@ -72616,7 +72624,7 @@
       <c r="C174" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="D174" s="46" t="s">
+      <c r="D174" s="45" t="s">
         <v>555</v>
       </c>
       <c r="E174" t="s">
@@ -72662,7 +72670,7 @@
       <c r="C175" s="1">
         <v>3264680009808</v>
       </c>
-      <c r="D175" s="46" t="s">
+      <c r="D175" s="45" t="s">
         <v>557</v>
       </c>
       <c r="E175" s="1">
@@ -72707,7 +72715,7 @@
       <c r="C176" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D176" s="46" t="s">
+      <c r="D176" s="45" t="s">
         <v>560</v>
       </c>
       <c r="E176" t="s">
@@ -72753,7 +72761,7 @@
       <c r="C177" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="D177" s="46" t="s">
+      <c r="D177" s="45" t="s">
         <v>564</v>
       </c>
       <c r="E177" s="1" t="s">
@@ -72798,7 +72806,7 @@
       <c r="C178" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D178" s="46" t="s">
+      <c r="D178" s="45" t="s">
         <v>568</v>
       </c>
       <c r="E178" t="s">
@@ -72843,7 +72851,7 @@
       <c r="C179" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="D179" s="46" t="s">
+      <c r="D179" s="45" t="s">
         <v>571</v>
       </c>
       <c r="E179" t="s">
@@ -72888,7 +72896,7 @@
       <c r="C180" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D180" s="46" t="s">
+      <c r="D180" s="45" t="s">
         <v>574</v>
       </c>
       <c r="E180" t="s">
@@ -72933,7 +72941,7 @@
       <c r="C181" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D181" s="46" t="s">
+      <c r="D181" s="45" t="s">
         <v>578</v>
       </c>
       <c r="E181" t="s">
@@ -72979,7 +72987,7 @@
       <c r="C182" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="D182" s="46" t="s">
+      <c r="D182" s="45" t="s">
         <v>581</v>
       </c>
       <c r="E182" s="1" t="s">
@@ -73024,7 +73032,7 @@
       <c r="C183" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D183" s="46" t="s">
+      <c r="D183" s="45" t="s">
         <v>585</v>
       </c>
       <c r="E183" t="s">
@@ -73069,7 +73077,7 @@
       <c r="C184" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D184" s="46" t="s">
+      <c r="D184" s="45" t="s">
         <v>588</v>
       </c>
       <c r="E184" t="s">
@@ -73117,7 +73125,7 @@
       <c r="C185" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="D185" s="46" t="s">
+      <c r="D185" s="45" t="s">
         <v>592</v>
       </c>
       <c r="E185" s="1" t="s">
@@ -73162,7 +73170,7 @@
       <c r="C186" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="D186" s="46" t="s">
+      <c r="D186" s="45" t="s">
         <v>596</v>
       </c>
       <c r="E186" t="s">
@@ -73207,7 +73215,7 @@
       <c r="C187" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="D187" s="46" t="s">
+      <c r="D187" s="45" t="s">
         <v>600</v>
       </c>
       <c r="E187" t="s">
@@ -73253,7 +73261,7 @@
       <c r="C188" s="1">
         <v>4902508103596</v>
       </c>
-      <c r="D188" s="46" t="s">
+      <c r="D188" s="45" t="s">
         <v>602</v>
       </c>
       <c r="E188" s="1">
@@ -73298,7 +73306,7 @@
       <c r="C189" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="D189" s="46" t="s">
+      <c r="D189" s="45" t="s">
         <v>605</v>
       </c>
       <c r="E189" t="s">
@@ -73344,7 +73352,7 @@
       <c r="C190" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="D190" s="46" t="s">
+      <c r="D190" s="45" t="s">
         <v>608</v>
       </c>
       <c r="E190" s="1" t="s">
@@ -73389,7 +73397,7 @@
       <c r="C191" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="D191" s="46" t="s">
+      <c r="D191" s="45" t="s">
         <v>611</v>
       </c>
       <c r="E191" t="s">
@@ -73434,7 +73442,7 @@
       <c r="C192" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="D192" s="46" t="s">
+      <c r="D192" s="45" t="s">
         <v>614</v>
       </c>
       <c r="E192" t="s">
@@ -73479,7 +73487,7 @@
       <c r="C193" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="D193" s="46" t="s">
+      <c r="D193" s="45" t="s">
         <v>617</v>
       </c>
       <c r="E193" t="s">
@@ -73524,7 +73532,7 @@
       <c r="C194" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="D194" s="46" t="s">
+      <c r="D194" s="45" t="s">
         <v>620</v>
       </c>
       <c r="E194" t="s">
@@ -73569,7 +73577,7 @@
       <c r="C195" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="D195" s="46" t="s">
+      <c r="D195" s="45" t="s">
         <v>624</v>
       </c>
       <c r="E195" t="s">
@@ -73614,7 +73622,7 @@
       <c r="C196" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="D196" s="46" t="s">
+      <c r="D196" s="45" t="s">
         <v>627</v>
       </c>
       <c r="E196" t="s">
@@ -73662,7 +73670,7 @@
       <c r="C197" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D197" s="46" t="s">
+      <c r="D197" s="45" t="s">
         <v>396</v>
       </c>
       <c r="E197" t="s">
@@ -73707,7 +73715,7 @@
       <c r="C198" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="D198" s="46">
+      <c r="D198" s="45">
         <v>4382</v>
       </c>
       <c r="E198" t="s">
@@ -73753,7 +73761,7 @@
       <c r="C199" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D199" s="46" t="s">
+      <c r="D199" s="45" t="s">
         <v>634</v>
       </c>
       <c r="E199" s="1" t="s">
@@ -73801,7 +73809,7 @@
       <c r="C200" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D200" s="46" t="s">
+      <c r="D200" s="45" t="s">
         <v>639</v>
       </c>
       <c r="E200" s="1" t="s">
@@ -73849,7 +73857,7 @@
       <c r="C201" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D201" s="46" t="s">
+      <c r="D201" s="45" t="s">
         <v>546</v>
       </c>
       <c r="E201" t="s">
@@ -73895,7 +73903,7 @@
       <c r="C202" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D202" s="46" t="s">
+      <c r="D202" s="45" t="s">
         <v>645</v>
       </c>
       <c r="E202" s="1" t="s">
@@ -73940,7 +73948,7 @@
       <c r="C203" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="D203" s="46" t="s">
+      <c r="D203" s="45" t="s">
         <v>648</v>
       </c>
       <c r="E203" t="s">
@@ -73985,7 +73993,7 @@
       <c r="C204" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="D204" s="46" t="s">
+      <c r="D204" s="45" t="s">
         <v>651</v>
       </c>
       <c r="E204" t="s">
@@ -74033,7 +74041,7 @@
       <c r="C205" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="D205" s="46" t="s">
+      <c r="D205" s="45" t="s">
         <v>655</v>
       </c>
       <c r="E205" t="s">
@@ -74078,7 +74086,7 @@
       <c r="C206" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="D206" s="46" t="s">
+      <c r="D206" s="45" t="s">
         <v>659</v>
       </c>
       <c r="E206" t="s">
@@ -74123,7 +74131,7 @@
       <c r="C207" s="1">
         <v>4571509303191</v>
       </c>
-      <c r="D207" s="46" t="s">
+      <c r="D207" s="45" t="s">
         <v>661</v>
       </c>
       <c r="E207">
@@ -74168,7 +74176,7 @@
       <c r="C208" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D208" s="46" t="s">
+      <c r="D208" s="45" t="s">
         <v>664</v>
       </c>
       <c r="E208" t="s">
@@ -74213,7 +74221,7 @@
       <c r="C209" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D209" s="46" t="s">
+      <c r="D209" s="45" t="s">
         <v>667</v>
       </c>
       <c r="E209" t="s">
@@ -74258,7 +74266,7 @@
       <c r="C210" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="D210" s="46" t="s">
+      <c r="D210" s="45" t="s">
         <v>671</v>
       </c>
       <c r="E210" t="s">
@@ -74303,7 +74311,7 @@
       <c r="C211" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="D211" s="46" t="s">
+      <c r="D211" s="45" t="s">
         <v>674</v>
       </c>
       <c r="E211" t="s">
@@ -74348,7 +74356,7 @@
       <c r="C212" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D212" s="46" t="s">
+      <c r="D212" s="45" t="s">
         <v>678</v>
       </c>
       <c r="E212" t="s">
@@ -74393,7 +74401,7 @@
       <c r="C213" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="D213" s="46" t="s">
+      <c r="D213" s="45" t="s">
         <v>681</v>
       </c>
       <c r="E213" t="s">
@@ -74438,7 +74446,7 @@
       <c r="C214" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="D214" s="46" t="s">
+      <c r="D214" s="45" t="s">
         <v>684</v>
       </c>
       <c r="E214" t="s">
@@ -74483,7 +74491,7 @@
       <c r="C215" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D215" s="46" t="s">
+      <c r="D215" s="45" t="s">
         <v>687</v>
       </c>
       <c r="E215" t="s">
@@ -74528,7 +74536,7 @@
       <c r="C216" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="D216" s="46" t="s">
+      <c r="D216" s="45" t="s">
         <v>691</v>
       </c>
       <c r="E216" t="s">
@@ -74573,7 +74581,7 @@
       <c r="C217" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="D217" s="46" t="s">
+      <c r="D217" s="45" t="s">
         <v>694</v>
       </c>
       <c r="E217" t="s">
@@ -74621,7 +74629,7 @@
       <c r="C218" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D218" s="46" t="s">
+      <c r="D218" s="45" t="s">
         <v>420</v>
       </c>
       <c r="E218" t="s">
@@ -74666,7 +74674,7 @@
       <c r="C219" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="D219" s="46" t="s">
+      <c r="D219" s="45" t="s">
         <v>699</v>
       </c>
       <c r="E219" t="s">
@@ -74712,7 +74720,7 @@
       <c r="C220" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D220" s="46" t="s">
+      <c r="D220" s="45" t="s">
         <v>702</v>
       </c>
       <c r="E220" s="1" t="s">
@@ -74757,7 +74765,7 @@
       <c r="C221" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D221" s="46" t="s">
+      <c r="D221" s="45" t="s">
         <v>705</v>
       </c>
       <c r="E221" t="s">
@@ -74802,7 +74810,7 @@
       <c r="C222" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="D222" s="46" t="s">
+      <c r="D222" s="45" t="s">
         <v>709</v>
       </c>
       <c r="E222" t="s">
@@ -74850,7 +74858,7 @@
       <c r="C223" s="1">
         <v>4550391062164</v>
       </c>
-      <c r="D223" s="46" t="s">
+      <c r="D223" s="45" t="s">
         <v>712</v>
       </c>
       <c r="E223">
@@ -74895,7 +74903,7 @@
       <c r="C224" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="D224" s="46">
+      <c r="D224" s="45">
         <v>616</v>
       </c>
       <c r="E224" t="s">
@@ -74943,7 +74951,7 @@
       <c r="C225" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D225" s="46" t="s">
+      <c r="D225" s="45" t="s">
         <v>420</v>
       </c>
       <c r="E225" t="s">
@@ -74989,7 +74997,7 @@
       <c r="C226" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="D226" s="46" t="s">
+      <c r="D226" s="45" t="s">
         <v>719</v>
       </c>
       <c r="E226" s="1" t="s">
@@ -75037,7 +75045,7 @@
       <c r="C227" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D227" s="46" t="s">
+      <c r="D227" s="45" t="s">
         <v>723</v>
       </c>
       <c r="E227" t="s">
@@ -75085,7 +75093,7 @@
       <c r="C228" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D228" s="46" t="s">
+      <c r="D228" s="45" t="s">
         <v>728</v>
       </c>
       <c r="E228" t="s">
@@ -75130,7 +75138,7 @@
       <c r="C229" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="D229" s="46" t="s">
+      <c r="D229" s="45" t="s">
         <v>732</v>
       </c>
       <c r="E229" t="s">
@@ -75176,7 +75184,7 @@
       <c r="C230" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D230" s="46" t="s">
+      <c r="D230" s="45" t="s">
         <v>735</v>
       </c>
       <c r="E230" s="1" t="s">
@@ -75221,7 +75229,7 @@
       <c r="C231" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="D231" s="46" t="s">
+      <c r="D231" s="45" t="s">
         <v>738</v>
       </c>
       <c r="E231" t="s">
@@ -75266,7 +75274,7 @@
       <c r="C232" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="D232" s="46" t="s">
+      <c r="D232" s="45" t="s">
         <v>742</v>
       </c>
       <c r="E232" t="s">
@@ -75311,7 +75319,7 @@
       <c r="C233" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D233" s="46" t="s">
+      <c r="D233" s="45" t="s">
         <v>745</v>
       </c>
       <c r="E233" t="s">
@@ -75356,7 +75364,7 @@
       <c r="C234" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="D234" s="46" t="s">
+      <c r="D234" s="45" t="s">
         <v>748</v>
       </c>
       <c r="E234" t="s">
@@ -75402,7 +75410,7 @@
       <c r="C235" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="D235" s="46" t="s">
+      <c r="D235" s="45" t="s">
         <v>751</v>
       </c>
       <c r="E235" s="1" t="s">
@@ -75447,7 +75455,7 @@
       <c r="C236" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="D236" s="46" t="s">
+      <c r="D236" s="45" t="s">
         <v>754</v>
       </c>
       <c r="E236" t="s">
@@ -75492,7 +75500,7 @@
       <c r="C237" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="D237" s="46" t="s">
+      <c r="D237" s="45" t="s">
         <v>758</v>
       </c>
       <c r="E237" t="s">
@@ -75537,7 +75545,7 @@
       <c r="C238" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="D238" s="46" t="s">
+      <c r="D238" s="45" t="s">
         <v>761</v>
       </c>
       <c r="E238" t="s">
@@ -75582,7 +75590,7 @@
       <c r="C239" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D239" s="46">
+      <c r="D239" s="45">
         <v>5060144645562</v>
       </c>
       <c r="E239" t="s">
@@ -75630,7 +75638,7 @@
       <c r="C240" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="D240" s="46" t="s">
+      <c r="D240" s="45" t="s">
         <v>768</v>
       </c>
       <c r="E240" t="s">
@@ -75675,7 +75683,7 @@
       <c r="C241" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="D241" s="46" t="s">
+      <c r="D241" s="45" t="s">
         <v>772</v>
       </c>
       <c r="E241" t="s">
@@ -75720,7 +75728,7 @@
       <c r="C242" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="D242" s="46" t="s">
+      <c r="D242" s="45" t="s">
         <v>776</v>
       </c>
       <c r="E242" t="s">
@@ -75765,7 +75773,7 @@
       <c r="C243" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D243" s="46" t="s">
+      <c r="D243" s="45" t="s">
         <v>780</v>
       </c>
       <c r="E243" t="s">
@@ -75810,7 +75818,7 @@
       <c r="C244" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="D244" s="46" t="s">
+      <c r="D244" s="45" t="s">
         <v>784</v>
       </c>
       <c r="E244" t="s">
@@ -75855,7 +75863,7 @@
       <c r="C245" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="D245" s="46" t="s">
+      <c r="D245" s="45" t="s">
         <v>787</v>
       </c>
       <c r="E245" t="s">
@@ -75900,7 +75908,7 @@
       <c r="C246" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="D246" s="46" t="s">
+      <c r="D246" s="45" t="s">
         <v>790</v>
       </c>
       <c r="E246" t="s">
@@ -75945,7 +75953,7 @@
       <c r="C247" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="D247" s="46" t="s">
+      <c r="D247" s="45" t="s">
         <v>793</v>
       </c>
       <c r="E247" t="s">
@@ -75990,7 +75998,7 @@
       <c r="C248" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="D248" s="46" t="s">
+      <c r="D248" s="45" t="s">
         <v>797</v>
       </c>
       <c r="E248" t="s">
@@ -76029,13 +76037,13 @@
       </c>
     </row>
     <row r="249" spans="1:15" ht="17" customHeight="1">
-      <c r="A249" s="1" t="s">
+      <c r="A249" s="46" t="s">
         <v>799</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="D249" s="46" t="s">
+      <c r="D249" s="45" t="s">
         <v>801</v>
       </c>
       <c r="E249" t="s">
@@ -76057,18 +76065,20 @@
         <f t="shared" si="12"/>
         <v>360</v>
       </c>
-      <c r="L249" s="41"/>
+      <c r="L249" s="6">
+        <v>610</v>
+      </c>
       <c r="M249" s="6">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>1220</v>
       </c>
       <c r="N249" s="6">
         <f t="shared" si="14"/>
-        <v>2040</v>
+        <v>820</v>
       </c>
       <c r="O249" s="8">
         <f t="shared" si="15"/>
-        <v>0.85</v>
+        <v>0.34166666666666667</v>
       </c>
     </row>
     <row r="250" spans="1:15" ht="17" customHeight="1">
@@ -76078,7 +76088,7 @@
       <c r="C250" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="D250" s="46" t="s">
+      <c r="D250" s="45" t="s">
         <v>804</v>
       </c>
       <c r="E250" t="s">
@@ -76123,7 +76133,7 @@
       <c r="C251" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D251" s="46" t="s">
+      <c r="D251" s="45" t="s">
         <v>807</v>
       </c>
       <c r="E251" t="s">
@@ -76171,7 +76181,7 @@
       <c r="C252" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D252" s="46" t="s">
+      <c r="D252" s="45" t="s">
         <v>728</v>
       </c>
       <c r="E252" t="s">
@@ -76217,7 +76227,7 @@
       <c r="C253" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D253" s="46" t="s">
+      <c r="D253" s="45" t="s">
         <v>812</v>
       </c>
       <c r="E253" s="1" t="s">
@@ -76262,7 +76272,7 @@
       <c r="C254" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="D254" s="46" t="s">
+      <c r="D254" s="45" t="s">
         <v>815</v>
       </c>
       <c r="E254" t="s">
@@ -76307,7 +76317,7 @@
       <c r="C255" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="D255" s="46">
+      <c r="D255" s="45">
         <v>4987176301543</v>
       </c>
       <c r="E255" t="s">
@@ -76352,7 +76362,7 @@
       <c r="C256" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="D256" s="46" t="s">
+      <c r="D256" s="45" t="s">
         <v>820</v>
       </c>
       <c r="E256" t="s">
@@ -76397,7 +76407,7 @@
       <c r="C257" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="D257" s="46" t="s">
+      <c r="D257" s="45" t="s">
         <v>823</v>
       </c>
       <c r="E257" t="s">
@@ -76442,7 +76452,7 @@
       <c r="C258" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="D258" s="46" t="s">
+      <c r="D258" s="45" t="s">
         <v>827</v>
       </c>
       <c r="E258" t="s">
@@ -76487,7 +76497,7 @@
       <c r="C259" s="1">
         <v>4550391012053</v>
       </c>
-      <c r="D259" s="46" t="s">
+      <c r="D259" s="45" t="s">
         <v>829</v>
       </c>
       <c r="E259">
@@ -76532,7 +76542,7 @@
       <c r="C260" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="D260" s="46" t="s">
+      <c r="D260" s="45" t="s">
         <v>832</v>
       </c>
       <c r="E260" t="s">
@@ -76577,7 +76587,7 @@
       <c r="C261" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="D261" s="46" t="s">
+      <c r="D261" s="45" t="s">
         <v>836</v>
       </c>
       <c r="E261" t="s">
@@ -76622,7 +76632,7 @@
       <c r="C262" s="1">
         <v>4550391011926</v>
       </c>
-      <c r="D262" s="46" t="s">
+      <c r="D262" s="45" t="s">
         <v>838</v>
       </c>
       <c r="E262">
@@ -76667,7 +76677,7 @@
       <c r="C263" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="D263" s="46" t="s">
+      <c r="D263" s="45" t="s">
         <v>841</v>
       </c>
       <c r="E263" t="s">
@@ -76712,7 +76722,7 @@
       <c r="C264" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="D264" s="46" t="s">
+      <c r="D264" s="45" t="s">
         <v>844</v>
       </c>
       <c r="E264" t="s">
@@ -76757,7 +76767,7 @@
       <c r="C265" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D265" s="46" t="s">
+      <c r="D265" s="45" t="s">
         <v>847</v>
       </c>
       <c r="E265" t="s">
@@ -76802,7 +76812,7 @@
       <c r="C266" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="D266" s="46" t="s">
+      <c r="D266" s="45" t="s">
         <v>850</v>
       </c>
       <c r="E266" t="s">
@@ -76847,7 +76857,7 @@
       <c r="C267" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="D267" s="46" t="s">
+      <c r="D267" s="45" t="s">
         <v>853</v>
       </c>
       <c r="E267" t="s">
@@ -76892,7 +76902,7 @@
       <c r="C268" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="D268" s="46" t="s">
+      <c r="D268" s="45" t="s">
         <v>856</v>
       </c>
       <c r="E268" t="s">
@@ -76937,7 +76947,7 @@
       <c r="C269" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="D269" s="46" t="s">
+      <c r="D269" s="45" t="s">
         <v>859</v>
       </c>
       <c r="E269" t="s">
@@ -76985,7 +76995,7 @@
       <c r="C270" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="D270" s="46" t="s">
+      <c r="D270" s="45" t="s">
         <v>863</v>
       </c>
       <c r="E270" t="s">
@@ -77030,7 +77040,7 @@
       <c r="C271" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D271" s="46" t="s">
+      <c r="D271" s="45" t="s">
         <v>867</v>
       </c>
       <c r="E271" t="s">
@@ -77075,7 +77085,7 @@
       <c r="C272" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="D272" s="46" t="s">
+      <c r="D272" s="45" t="s">
         <v>870</v>
       </c>
       <c r="E272" t="s">
@@ -77123,7 +77133,7 @@
       <c r="C273" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="D273" s="46" t="s">
+      <c r="D273" s="45" t="s">
         <v>874</v>
       </c>
       <c r="E273" t="s">
@@ -77171,7 +77181,7 @@
       <c r="C274" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D274" s="46" t="s">
+      <c r="D274" s="45" t="s">
         <v>639</v>
       </c>
       <c r="E274" t="s">
@@ -77216,7 +77226,7 @@
       <c r="C275" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="D275" s="46" t="s">
+      <c r="D275" s="45" t="s">
         <v>880</v>
       </c>
       <c r="E275" t="s">
@@ -77264,7 +77274,7 @@
       <c r="C276" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D276" s="46" t="s">
+      <c r="D276" s="45" t="s">
         <v>728</v>
       </c>
       <c r="E276" t="s">
@@ -77312,7 +77322,7 @@
       <c r="C277" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D277" s="46" t="s">
+      <c r="D277" s="45" t="s">
         <v>639</v>
       </c>
       <c r="E277" t="s">
@@ -77360,7 +77370,7 @@
       <c r="C278" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D278" s="46" t="s">
+      <c r="D278" s="45" t="s">
         <v>639</v>
       </c>
       <c r="E278" s="1" t="s">
@@ -77405,7 +77415,7 @@
       <c r="C279" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="D279" s="46" t="s">
+      <c r="D279" s="45" t="s">
         <v>889</v>
       </c>
       <c r="E279" t="s">
@@ -77450,7 +77460,7 @@
       <c r="C280" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="D280" s="46" t="s">
+      <c r="D280" s="45" t="s">
         <v>893</v>
       </c>
       <c r="E280" t="s">
@@ -77495,7 +77505,7 @@
       <c r="C281" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="D281" s="46" t="s">
+      <c r="D281" s="45" t="s">
         <v>896</v>
       </c>
       <c r="E281" t="s">
@@ -77540,7 +77550,7 @@
       <c r="C282" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="D282" s="46" t="s">
+      <c r="D282" s="45" t="s">
         <v>493</v>
       </c>
       <c r="E282" t="s">
@@ -77585,7 +77595,7 @@
       <c r="C283" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="D283" s="46">
+      <c r="D283" s="45">
         <v>720</v>
       </c>
       <c r="E283" t="s">
@@ -77630,7 +77640,7 @@
       <c r="C284" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="D284" s="46" t="s">
+      <c r="D284" s="45" t="s">
         <v>903</v>
       </c>
       <c r="E284" t="s">
@@ -77676,7 +77686,7 @@
       <c r="C285" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="D285" s="46" t="s">
+      <c r="D285" s="45" t="s">
         <v>906</v>
       </c>
       <c r="E285" s="1" t="s">
@@ -77721,7 +77731,7 @@
       <c r="C286" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="D286" s="46" t="s">
+      <c r="D286" s="45" t="s">
         <v>909</v>
       </c>
       <c r="E286" t="s">
@@ -77767,7 +77777,7 @@
       <c r="C287" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="D287" s="46" t="s">
+      <c r="D287" s="45" t="s">
         <v>912</v>
       </c>
       <c r="E287" s="1" t="s">
@@ -77812,7 +77822,7 @@
       <c r="C288" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="D288" s="46" t="s">
+      <c r="D288" s="45" t="s">
         <v>915</v>
       </c>
       <c r="E288" t="s">
@@ -77857,7 +77867,7 @@
       <c r="C289" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="D289" s="46" t="s">
+      <c r="D289" s="45" t="s">
         <v>918</v>
       </c>
       <c r="E289" t="s">
@@ -77903,7 +77913,7 @@
       <c r="C290" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="D290" s="46" t="s">
+      <c r="D290" s="45" t="s">
         <v>922</v>
       </c>
       <c r="E290" s="1" t="s">
@@ -77948,7 +77958,7 @@
       <c r="C291" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="D291" s="46" t="s">
+      <c r="D291" s="45" t="s">
         <v>925</v>
       </c>
       <c r="E291" t="s">
@@ -77994,7 +78004,7 @@
       <c r="C292" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="D292" s="46" t="s">
+      <c r="D292" s="45" t="s">
         <v>929</v>
       </c>
       <c r="E292" s="1" t="s">
@@ -78039,7 +78049,7 @@
       <c r="C293" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="D293" s="46" t="s">
+      <c r="D293" s="45" t="s">
         <v>932</v>
       </c>
       <c r="E293" t="s">
@@ -78085,7 +78095,7 @@
       <c r="C294" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="D294" s="46" t="s">
+      <c r="D294" s="45" t="s">
         <v>936</v>
       </c>
       <c r="E294" s="1" t="s">
@@ -78130,7 +78140,7 @@
       <c r="C295" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="D295" s="46">
+      <c r="D295" s="45">
         <v>199</v>
       </c>
       <c r="E295" t="s">
@@ -78175,7 +78185,7 @@
       <c r="C296" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="D296" s="46" t="s">
+      <c r="D296" s="45" t="s">
         <v>941</v>
       </c>
       <c r="E296" t="s">
@@ -78221,7 +78231,7 @@
       <c r="C297" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="D297" s="46" t="s">
+      <c r="D297" s="45" t="s">
         <v>944</v>
       </c>
       <c r="E297" s="1" t="s">
@@ -78266,7 +78276,7 @@
       <c r="C298" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="D298" s="46" t="s">
+      <c r="D298" s="45" t="s">
         <v>947</v>
       </c>
       <c r="E298" t="s">
@@ -78311,7 +78321,7 @@
       <c r="C299" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="D299" s="46" t="s">
+      <c r="D299" s="45" t="s">
         <v>951</v>
       </c>
       <c r="E299" t="s">
@@ -78356,7 +78366,7 @@
       <c r="C300" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="D300" s="46" t="s">
+      <c r="D300" s="45" t="s">
         <v>954</v>
       </c>
       <c r="E300" t="s">
@@ -78413,15 +78423,15 @@
       </c>
       <c r="M301" s="1">
         <f>SUM(M7:M300)</f>
-        <v>1823065</v>
+        <v>1824285</v>
       </c>
       <c r="N301" s="1">
         <f>SUM(N7:N300)</f>
-        <v>995716.05000000028</v>
+        <v>994496.05000000028</v>
       </c>
       <c r="O301" s="8">
         <f t="shared" si="19"/>
-        <v>0.3002569647968934</v>
+        <v>0.29988907527954334</v>
       </c>
     </row>
     <row r="302" spans="1:15" ht="17" customHeight="1"/>
@@ -78429,7 +78439,7 @@
       <c r="M303" s="30" t="s">
         <v>956</v>
       </c>
-      <c r="N303" s="42"/>
+      <c r="N303" s="41"/>
       <c r="O303" s="32">
         <f>SUM(N303/I301)</f>
         <v>0</v>
@@ -78439,7 +78449,7 @@
       <c r="M304" s="33" t="s">
         <v>957</v>
       </c>
-      <c r="N304" s="43"/>
+      <c r="N304" s="42"/>
       <c r="O304" s="34">
         <f>SUM(N304/I301)</f>
         <v>0</v>
@@ -78449,7 +78459,7 @@
       <c r="M305" s="33" t="s">
         <v>958</v>
       </c>
-      <c r="N305" s="43"/>
+      <c r="N305" s="42"/>
       <c r="O305" s="34">
         <f>SUM(N305/I301)</f>
         <v>0</v>
@@ -78459,7 +78469,7 @@
       <c r="M306" s="33" t="s">
         <v>959</v>
       </c>
-      <c r="N306" s="43"/>
+      <c r="N306" s="42"/>
       <c r="O306" s="35"/>
     </row>
     <row r="307" spans="13:15" ht="17" customHeight="1">
@@ -78484,7 +78494,7 @@
       <c r="M309" s="33" t="s">
         <v>961</v>
       </c>
-      <c r="N309" s="43"/>
+      <c r="N309" s="42"/>
       <c r="O309" s="34">
         <f>SUM(N309/I301)</f>
         <v>0</v>
@@ -78494,7 +78504,7 @@
       <c r="M310" s="36" t="s">
         <v>962</v>
       </c>
-      <c r="N310" s="44"/>
+      <c r="N310" s="43"/>
       <c r="O310" s="34">
         <f>SUM(N310/I301)</f>
         <v>0</v>
@@ -78524,7 +78534,7 @@
       </c>
       <c r="N313" s="28">
         <f>SUM(N301-N307-N311)</f>
-        <v>995716.05000000028</v>
+        <v>994496.05000000028</v>
       </c>
       <c r="O313" s="35"/>
     </row>
@@ -78534,7 +78544,7 @@
       </c>
       <c r="N314" s="38">
         <f>IF(I301=0,"",N313/I301)</f>
-        <v>0.3002569647968934</v>
+        <v>0.29988907527954334</v>
       </c>
       <c r="O314" s="39"/>
     </row>

--- a/MomijiStore_OS/02_Analytics/SourceData/楽天運営 KPI管理シート.xlsx
+++ b/MomijiStore_OS/02_Analytics/SourceData/楽天運営 KPI管理シート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hide0726/Desktop/Claude Code/MomijiStore_OS/02_Analytics/SourceData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_92CD296F0687250FB87CF8C0F4C503A5F002C1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F49CE9C-E2FD-2347-874D-E962278C2C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8300" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4月" sheetId="1" r:id="rId1"/>
@@ -19647,15 +19647,15 @@
         <v>504</v>
       </c>
       <c r="M264" s="6">
-        <f t="shared" ref="M264:M327" si="17">SUM(H264*L264)</f>
+        <f t="shared" ref="M264:M293" si="17">SUM(H264*L264)</f>
         <v>504</v>
       </c>
       <c r="N264" s="6">
-        <f t="shared" ref="N264:N327" si="18">SUM(I264-K264-M264)</f>
+        <f t="shared" ref="N264:N293" si="18">SUM(I264-K264-M264)</f>
         <v>754</v>
       </c>
       <c r="O264" s="8">
-        <f t="shared" ref="O264:O327" si="19">IF(I264=0,"",N264/I264)</f>
+        <f t="shared" ref="O264:O294" si="19">IF(I264=0,"",N264/I264)</f>
         <v>0.50945945945945947</v>
       </c>
     </row>
@@ -36535,15 +36535,15 @@
         <v>1116</v>
       </c>
       <c r="M264" s="6">
-        <f t="shared" ref="M264:M327" si="17">SUM(H264*L264)</f>
+        <f t="shared" ref="M264:M320" si="17">SUM(H264*L264)</f>
         <v>1116</v>
       </c>
       <c r="N264" s="6">
-        <f t="shared" ref="N264:N327" si="18">SUM(I264-K264-M264)</f>
+        <f t="shared" ref="N264:N320" si="18">SUM(I264-K264-M264)</f>
         <v>992</v>
       </c>
       <c r="O264" s="8">
-        <f t="shared" ref="O264:O327" si="19">IF(I264=0,"",N264/I264)</f>
+        <f t="shared" ref="O264:O322" si="19">IF(I264=0,"",N264/I264)</f>
         <v>0.4</v>
       </c>
     </row>
@@ -51539,15 +51539,15 @@
       </c>
       <c r="L992" s="6"/>
       <c r="M992" s="6">
-        <f t="shared" ref="M992:M1055" si="61">SUM(H992*L992)</f>
+        <f t="shared" ref="M992:M1000" si="61">SUM(H992*L992)</f>
         <v>0</v>
       </c>
       <c r="N992" s="6">
-        <f t="shared" ref="N992:N1055" si="62">SUM(I992-K992-M992)</f>
+        <f t="shared" ref="N992:N1000" si="62">SUM(I992-K992-M992)</f>
         <v>0</v>
       </c>
       <c r="O992" s="8" t="str">
-        <f t="shared" ref="O992:O1055" si="63">IF(I992=0,"",N992/I992)</f>
+        <f t="shared" ref="O992:O1000" si="63">IF(I992=0,"",N992/I992)</f>
         <v/>
       </c>
     </row>
@@ -62868,15 +62868,15 @@
         <v>825</v>
       </c>
       <c r="M264" s="6">
-        <f t="shared" ref="M264:M327" si="17">SUM(H264*L264)</f>
+        <f t="shared" ref="M264:M308" si="17">SUM(H264*L264)</f>
         <v>825</v>
       </c>
       <c r="N264" s="6">
-        <f t="shared" ref="N264:N327" si="18">SUM(I264-K264-M264)</f>
+        <f t="shared" ref="N264:N308" si="18">SUM(I264-K264-M264)</f>
         <v>1113</v>
       </c>
       <c r="O264" s="8">
-        <f t="shared" ref="O264:O327" si="19">IF(I264=0,"",N264/I264)</f>
+        <f t="shared" ref="O264:O309" si="19">IF(I264=0,"",N264/I264)</f>
         <v>0.48815789473684212</v>
       </c>
     </row>
@@ -76748,15 +76748,15 @@
         <v>858</v>
       </c>
       <c r="M264" s="6">
-        <f t="shared" ref="M264:M327" si="17">SUM(H264*L264)</f>
+        <f t="shared" ref="M264:M300" si="17">SUM(H264*L264)</f>
         <v>858</v>
       </c>
       <c r="N264" s="6">
-        <f t="shared" ref="N264:N327" si="18">SUM(I264-K264-M264)</f>
+        <f t="shared" ref="N264:N300" si="18">SUM(I264-K264-M264)</f>
         <v>825</v>
       </c>
       <c r="O264" s="8">
-        <f t="shared" ref="O264:O327" si="19">IF(I264=0,"",N264/I264)</f>
+        <f t="shared" ref="O264:O301" si="19">IF(I264=0,"",N264/I264)</f>
         <v>0.41666666666666669</v>
       </c>
     </row>
@@ -78439,37 +78439,45 @@
       <c r="M303" s="30" t="s">
         <v>956</v>
       </c>
-      <c r="N303" s="41"/>
+      <c r="N303" s="41">
+        <v>76791</v>
+      </c>
       <c r="O303" s="32">
         <f>SUM(N303/I301)</f>
-        <v>0</v>
+        <v>2.3156232726908674E-2</v>
       </c>
     </row>
     <row r="304" spans="1:15" ht="17" customHeight="1">
       <c r="M304" s="33" t="s">
         <v>957</v>
       </c>
-      <c r="N304" s="42"/>
+      <c r="N304" s="42">
+        <v>96798</v>
+      </c>
       <c r="O304" s="34">
         <f>SUM(N304/I301)</f>
-        <v>0</v>
+        <v>2.9189319262664975E-2</v>
       </c>
     </row>
     <row r="305" spans="13:15" ht="17" customHeight="1">
       <c r="M305" s="33" t="s">
         <v>958</v>
       </c>
-      <c r="N305" s="42"/>
+      <c r="N305" s="42">
+        <v>11700</v>
+      </c>
       <c r="O305" s="34">
         <f>SUM(N305/I301)</f>
-        <v>0</v>
+        <v>3.528120781144034E-3</v>
       </c>
     </row>
     <row r="306" spans="13:15" ht="17" customHeight="1">
       <c r="M306" s="33" t="s">
         <v>959</v>
       </c>
-      <c r="N306" s="42"/>
+      <c r="N306" s="42">
+        <v>0</v>
+      </c>
       <c r="O306" s="35"/>
     </row>
     <row r="307" spans="13:15" ht="17" customHeight="1">
@@ -78478,11 +78486,11 @@
       </c>
       <c r="N307" s="28">
         <f>SUM(N303:N306)</f>
-        <v>0</v>
+        <v>185289</v>
       </c>
       <c r="O307" s="34">
         <f>SUM(N307/I301)</f>
-        <v>0</v>
+        <v>5.5873672770717683E-2</v>
       </c>
     </row>
     <row r="308" spans="13:15" ht="17" customHeight="1">
@@ -78494,20 +78502,24 @@
       <c r="M309" s="33" t="s">
         <v>961</v>
       </c>
-      <c r="N309" s="42"/>
+      <c r="N309" s="42">
+        <v>248314</v>
+      </c>
       <c r="O309" s="34">
         <f>SUM(N309/I301)</f>
-        <v>0</v>
+        <v>7.4878784927264921E-2</v>
       </c>
     </row>
     <row r="310" spans="13:15" ht="13" customHeight="1">
       <c r="M310" s="36" t="s">
         <v>962</v>
       </c>
-      <c r="N310" s="43"/>
+      <c r="N310" s="43">
+        <v>36608</v>
+      </c>
       <c r="O310" s="34">
         <f>SUM(N310/I301)</f>
-        <v>0</v>
+        <v>1.1039097910779555E-2</v>
       </c>
     </row>
     <row r="311" spans="13:15" ht="13" customHeight="1">
@@ -78516,11 +78528,11 @@
       </c>
       <c r="N311" s="1">
         <f>SUM(N309:N310)</f>
-        <v>0</v>
+        <v>284922</v>
       </c>
       <c r="O311" s="34">
         <f>SUM(O309:O310)</f>
-        <v>0</v>
+        <v>8.5917882838044482E-2</v>
       </c>
     </row>
     <row r="312" spans="13:15" ht="13" customHeight="1">
@@ -78534,7 +78546,7 @@
       </c>
       <c r="N313" s="28">
         <f>SUM(N301-N307-N311)</f>
-        <v>994496.05000000028</v>
+        <v>524285.05000000028</v>
       </c>
       <c r="O313" s="35"/>
     </row>
@@ -78544,7 +78556,7 @@
       </c>
       <c r="N314" s="38">
         <f>IF(I301=0,"",N313/I301)</f>
-        <v>0.29988907527954334</v>
+        <v>0.15809751967078117</v>
       </c>
       <c r="O314" s="39"/>
     </row>

--- a/MomijiStore_OS/02_Analytics/SourceData/楽天運営 KPI管理シート.xlsx
+++ b/MomijiStore_OS/02_Analytics/SourceData/楽天運営 KPI管理シート.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hide0726/Desktop/Claude Code/MomijiStore_OS/02_Analytics/SourceData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F49CE9C-E2FD-2347-874D-E962278C2C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F047B47-AF67-F24B-8F5D-7EC808BCE99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8300" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6813,7 +6813,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6836,11 +6836,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD4D4D4"/>
         <bgColor rgb="FFD4D4D4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -7025,12 +7020,12 @@
     <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -64948,7 +64943,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="29" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="44" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" style="41" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -65000,7 +64995,7 @@
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D7" s="42" t="s">
         <v>12</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -65044,7 +65039,7 @@
       <c r="C8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="42" t="s">
         <v>26</v>
       </c>
       <c r="E8" t="s">
@@ -65089,7 +65084,7 @@
       <c r="C9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="42" t="s">
         <v>29</v>
       </c>
       <c r="E9" t="s">
@@ -65134,7 +65129,7 @@
       <c r="C10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="45" t="s">
+      <c r="D10" s="42" t="s">
         <v>33</v>
       </c>
       <c r="E10" t="s">
@@ -65179,7 +65174,7 @@
       <c r="C11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="42">
         <v>4902430898706</v>
       </c>
       <c r="E11" t="s">
@@ -65224,7 +65219,7 @@
       <c r="C12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="42" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
@@ -65270,7 +65265,7 @@
       <c r="C13" s="1">
         <v>4550391012121</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="42" t="s">
         <v>41</v>
       </c>
       <c r="E13" s="1">
@@ -65315,7 +65310,7 @@
       <c r="C14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D14" s="42" t="s">
         <v>44</v>
       </c>
       <c r="E14" t="s">
@@ -65360,7 +65355,7 @@
       <c r="C15" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D15" s="42" t="s">
         <v>48</v>
       </c>
       <c r="E15" t="s">
@@ -65405,7 +65400,7 @@
       <c r="C16" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="42">
         <v>36300</v>
       </c>
       <c r="E16" t="s">
@@ -65453,7 +65448,7 @@
       <c r="C17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D17" s="42" t="s">
         <v>54</v>
       </c>
       <c r="E17" t="s">
@@ -65498,7 +65493,7 @@
       <c r="C18" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="42" t="s">
         <v>58</v>
       </c>
       <c r="E18" t="s">
@@ -65543,7 +65538,7 @@
       <c r="C19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D19" s="42" t="s">
         <v>61</v>
       </c>
       <c r="E19" t="s">
@@ -65588,7 +65583,7 @@
       <c r="C20" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="42" t="s">
         <v>64</v>
       </c>
       <c r="E20" t="s">
@@ -65633,7 +65628,7 @@
       <c r="C21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D21" s="42" t="s">
         <v>67</v>
       </c>
       <c r="E21" t="s">
@@ -65678,7 +65673,7 @@
       <c r="C22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="42" t="s">
         <v>70</v>
       </c>
       <c r="E22" t="s">
@@ -65723,7 +65718,7 @@
       <c r="C23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="42" t="s">
         <v>74</v>
       </c>
       <c r="E23" t="s">
@@ -65768,7 +65763,7 @@
       <c r="C24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="42" t="s">
         <v>77</v>
       </c>
       <c r="E24" t="s">
@@ -65816,7 +65811,7 @@
       <c r="C25" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D25" s="42" t="s">
         <v>80</v>
       </c>
       <c r="E25" t="s">
@@ -65861,7 +65856,7 @@
       <c r="C26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="45">
+      <c r="D26" s="42">
         <v>9524</v>
       </c>
       <c r="E26" t="s">
@@ -65906,7 +65901,7 @@
       <c r="C27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D27" s="42" t="s">
         <v>86</v>
       </c>
       <c r="E27" t="s">
@@ -65951,7 +65946,7 @@
       <c r="C28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="42" t="s">
         <v>89</v>
       </c>
       <c r="E28" t="s">
@@ -65999,7 +65994,7 @@
       <c r="C29" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="42" t="s">
         <v>92</v>
       </c>
       <c r="E29" t="s">
@@ -66045,7 +66040,7 @@
       <c r="C30" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="42" t="s">
         <v>96</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -66090,7 +66085,7 @@
       <c r="C31" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D31" s="45">
+      <c r="D31" s="42">
         <v>840414639447</v>
       </c>
       <c r="E31" t="s">
@@ -66135,7 +66130,7 @@
       <c r="C32" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D32" s="45" t="s">
+      <c r="D32" s="42" t="s">
         <v>102</v>
       </c>
       <c r="E32" t="s">
@@ -66180,7 +66175,7 @@
       <c r="C33" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D33" s="45" t="s">
+      <c r="D33" s="42" t="s">
         <v>105</v>
       </c>
       <c r="E33" t="s">
@@ -66225,7 +66220,7 @@
       <c r="C34" s="1">
         <v>4550391042821</v>
       </c>
-      <c r="D34" s="45" t="s">
+      <c r="D34" s="42" t="s">
         <v>107</v>
       </c>
       <c r="E34">
@@ -66271,7 +66266,7 @@
       <c r="C35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="45" t="s">
+      <c r="D35" s="42" t="s">
         <v>110</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -66317,7 +66312,7 @@
       <c r="C36" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D36" s="45">
+      <c r="D36" s="42">
         <v>2486</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -66363,7 +66358,7 @@
       <c r="C37" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D37" s="45" t="s">
+      <c r="D37" s="42" t="s">
         <v>116</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -66409,7 +66404,7 @@
       <c r="C38" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D38" s="45" t="s">
+      <c r="D38" s="42" t="s">
         <v>119</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -66454,7 +66449,7 @@
       <c r="C39" s="1">
         <v>3264680024993</v>
       </c>
-      <c r="D39" s="45" t="s">
+      <c r="D39" s="42" t="s">
         <v>121</v>
       </c>
       <c r="E39">
@@ -66499,7 +66494,7 @@
       <c r="C40" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D40" s="45" t="s">
+      <c r="D40" s="42" t="s">
         <v>124</v>
       </c>
       <c r="E40" t="s">
@@ -66547,7 +66542,7 @@
       <c r="C41" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D41" s="45" t="s">
+      <c r="D41" s="42" t="s">
         <v>54</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -66595,7 +66590,7 @@
       <c r="C42" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D42" s="45" t="s">
+      <c r="D42" s="42" t="s">
         <v>130</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -66640,7 +66635,7 @@
       <c r="C43" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D43" s="45" t="s">
+      <c r="D43" s="42" t="s">
         <v>134</v>
       </c>
       <c r="E43" t="s">
@@ -66685,7 +66680,7 @@
       <c r="C44" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D44" s="45" t="s">
+      <c r="D44" s="42" t="s">
         <v>137</v>
       </c>
       <c r="E44" t="s">
@@ -66730,7 +66725,7 @@
       <c r="C45" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D45" s="45" t="s">
+      <c r="D45" s="42" t="s">
         <v>140</v>
       </c>
       <c r="E45" t="s">
@@ -66775,7 +66770,7 @@
       <c r="C46" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D46" s="45" t="s">
+      <c r="D46" s="42" t="s">
         <v>143</v>
       </c>
       <c r="E46" t="s">
@@ -66820,7 +66815,7 @@
       <c r="C47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="45" t="s">
+      <c r="D47" s="42" t="s">
         <v>146</v>
       </c>
       <c r="E47" t="s">
@@ -66865,7 +66860,7 @@
       <c r="C48" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D48" s="45" t="s">
+      <c r="D48" s="42" t="s">
         <v>149</v>
       </c>
       <c r="E48" t="s">
@@ -66913,7 +66908,7 @@
       <c r="C49" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="45" t="s">
+      <c r="D49" s="42" t="s">
         <v>153</v>
       </c>
       <c r="E49" t="s">
@@ -66961,7 +66956,7 @@
       <c r="C50" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="45" t="s">
+      <c r="D50" s="42" t="s">
         <v>153</v>
       </c>
       <c r="E50" t="s">
@@ -67006,7 +67001,7 @@
       <c r="C51" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D51" s="45" t="s">
+      <c r="D51" s="42" t="s">
         <v>159</v>
       </c>
       <c r="E51" t="s">
@@ -67051,7 +67046,7 @@
       <c r="C52" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D52" s="45" t="s">
+      <c r="D52" s="42" t="s">
         <v>163</v>
       </c>
       <c r="E52" t="s">
@@ -67097,7 +67092,7 @@
       <c r="C53" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D53" s="45" t="s">
+      <c r="D53" s="42" t="s">
         <v>166</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -67145,7 +67140,7 @@
       <c r="C54" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D54" s="45" t="s">
+      <c r="D54" s="42" t="s">
         <v>170</v>
       </c>
       <c r="E54" t="s">
@@ -67190,7 +67185,7 @@
       <c r="C55" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D55" s="45" t="s">
+      <c r="D55" s="42" t="s">
         <v>174</v>
       </c>
       <c r="E55" t="s">
@@ -67236,7 +67231,7 @@
       <c r="C56" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D56" s="45" t="s">
+      <c r="D56" s="42" t="s">
         <v>177</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -67281,7 +67276,7 @@
       <c r="C57" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="42" t="s">
         <v>180</v>
       </c>
       <c r="E57" t="s">
@@ -67326,7 +67321,7 @@
       <c r="C58" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D58" s="45" t="s">
+      <c r="D58" s="42" t="s">
         <v>183</v>
       </c>
       <c r="E58" t="s">
@@ -67372,7 +67367,7 @@
       <c r="C59" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="45" t="s">
+      <c r="D59" s="42" t="s">
         <v>187</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -67417,7 +67412,7 @@
       <c r="C60" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D60" s="45" t="s">
+      <c r="D60" s="42" t="s">
         <v>191</v>
       </c>
       <c r="E60" t="s">
@@ -67463,7 +67458,7 @@
       <c r="C61" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D61" s="45" t="s">
+      <c r="D61" s="42" t="s">
         <v>194</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -67508,7 +67503,7 @@
       <c r="C62" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D62" s="45" t="s">
+      <c r="D62" s="42" t="s">
         <v>198</v>
       </c>
       <c r="E62" t="s">
@@ -67556,7 +67551,7 @@
       <c r="C63" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D63" s="45" t="s">
+      <c r="D63" s="42" t="s">
         <v>202</v>
       </c>
       <c r="E63" t="s">
@@ -67601,7 +67596,7 @@
       <c r="C64" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D64" s="45" t="s">
+      <c r="D64" s="42" t="s">
         <v>206</v>
       </c>
       <c r="E64" t="s">
@@ -67646,7 +67641,7 @@
       <c r="C65" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D65" s="45" t="s">
+      <c r="D65" s="42" t="s">
         <v>209</v>
       </c>
       <c r="E65" t="s">
@@ -67691,7 +67686,7 @@
       <c r="C66" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D66" s="45" t="s">
+      <c r="D66" s="42" t="s">
         <v>212</v>
       </c>
       <c r="E66" t="s">
@@ -67736,7 +67731,7 @@
       <c r="C67" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D67" s="45" t="s">
+      <c r="D67" s="42" t="s">
         <v>215</v>
       </c>
       <c r="E67" t="s">
@@ -67781,7 +67776,7 @@
       <c r="C68" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D68" s="45" t="s">
+      <c r="D68" s="42" t="s">
         <v>218</v>
       </c>
       <c r="E68" t="s">
@@ -67829,7 +67824,7 @@
       <c r="C69" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D69" s="45" t="s">
+      <c r="D69" s="42" t="s">
         <v>221</v>
       </c>
       <c r="E69" t="s">
@@ -67874,7 +67869,7 @@
       <c r="C70" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D70" s="45" t="s">
+      <c r="D70" s="42" t="s">
         <v>225</v>
       </c>
       <c r="E70" t="s">
@@ -67919,7 +67914,7 @@
       <c r="C71" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D71" s="45" t="s">
+      <c r="D71" s="42" t="s">
         <v>228</v>
       </c>
       <c r="E71" t="s">
@@ -67964,7 +67959,7 @@
       <c r="C72" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D72" s="45" t="s">
+      <c r="D72" s="42" t="s">
         <v>231</v>
       </c>
       <c r="E72" t="s">
@@ -68009,7 +68004,7 @@
       <c r="C73" s="1">
         <v>4550391911226</v>
       </c>
-      <c r="D73" s="45" t="s">
+      <c r="D73" s="42" t="s">
         <v>234</v>
       </c>
       <c r="E73">
@@ -68054,7 +68049,7 @@
       <c r="C74" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D74" s="45" t="s">
+      <c r="D74" s="42" t="s">
         <v>237</v>
       </c>
       <c r="E74" t="s">
@@ -68099,7 +68094,7 @@
       <c r="C75" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D75" s="45" t="s">
+      <c r="D75" s="42" t="s">
         <v>240</v>
       </c>
       <c r="E75" t="s">
@@ -68144,7 +68139,7 @@
       <c r="C76" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D76" s="45" t="s">
+      <c r="D76" s="42" t="s">
         <v>243</v>
       </c>
       <c r="E76" t="s">
@@ -68189,7 +68184,7 @@
       <c r="C77" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D77" s="45" t="s">
+      <c r="D77" s="42" t="s">
         <v>246</v>
       </c>
       <c r="E77" t="s">
@@ -68234,7 +68229,7 @@
       <c r="C78" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D78" s="45" t="s">
+      <c r="D78" s="42" t="s">
         <v>249</v>
       </c>
       <c r="E78" t="s">
@@ -68279,7 +68274,7 @@
       <c r="C79" s="1">
         <v>4550391910564</v>
       </c>
-      <c r="D79" s="45" t="s">
+      <c r="D79" s="42" t="s">
         <v>252</v>
       </c>
       <c r="E79">
@@ -68324,7 +68319,7 @@
       <c r="C80" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D80" s="45" t="s">
+      <c r="D80" s="42" t="s">
         <v>255</v>
       </c>
       <c r="E80" t="s">
@@ -68369,7 +68364,7 @@
       <c r="C81" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D81" s="45">
+      <c r="D81" s="42">
         <v>4571263111773</v>
       </c>
       <c r="E81" t="s">
@@ -68415,7 +68410,7 @@
       <c r="C82" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D82" s="45" t="s">
+      <c r="D82" s="42" t="s">
         <v>260</v>
       </c>
       <c r="E82" s="1" t="s">
@@ -68460,7 +68455,7 @@
       <c r="C83" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D83" s="45" t="s">
+      <c r="D83" s="42" t="s">
         <v>263</v>
       </c>
       <c r="E83" t="s">
@@ -68505,7 +68500,7 @@
       <c r="C84" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D84" s="45">
+      <c r="D84" s="42">
         <v>4901133718984</v>
       </c>
       <c r="E84" t="s">
@@ -68553,7 +68548,7 @@
       <c r="C85" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D85" s="45" t="s">
+      <c r="D85" s="42" t="s">
         <v>270</v>
       </c>
       <c r="E85" t="s">
@@ -68601,7 +68596,7 @@
       <c r="C86" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D86" s="45">
+      <c r="D86" s="42">
         <v>7480</v>
       </c>
       <c r="E86" s="1" t="s">
@@ -68646,7 +68641,7 @@
       <c r="C87" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D87" s="45" t="s">
+      <c r="D87" s="42" t="s">
         <v>278</v>
       </c>
       <c r="E87" t="s">
@@ -68691,7 +68686,7 @@
       <c r="C88" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D88" s="45" t="s">
+      <c r="D88" s="42" t="s">
         <v>281</v>
       </c>
       <c r="E88" t="s">
@@ -68736,7 +68731,7 @@
       <c r="C89" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D89" s="45" t="s">
+      <c r="D89" s="42" t="s">
         <v>284</v>
       </c>
       <c r="E89" t="s">
@@ -68784,7 +68779,7 @@
       <c r="C90" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="D90" s="45">
+      <c r="D90" s="42">
         <v>194644137595</v>
       </c>
       <c r="E90" t="s">
@@ -68832,7 +68827,7 @@
       <c r="C91" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D91" s="45" t="s">
+      <c r="D91" s="42" t="s">
         <v>291</v>
       </c>
       <c r="E91" t="s">
@@ -68877,7 +68872,7 @@
       <c r="C92" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D92" s="45" t="s">
+      <c r="D92" s="42" t="s">
         <v>295</v>
       </c>
       <c r="E92" t="s">
@@ -68922,7 +68917,7 @@
       <c r="C93" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D93" s="45" t="s">
+      <c r="D93" s="42" t="s">
         <v>298</v>
       </c>
       <c r="E93" t="s">
@@ -68967,7 +68962,7 @@
       <c r="C94" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="D94" s="45" t="s">
+      <c r="D94" s="42" t="s">
         <v>301</v>
       </c>
       <c r="E94" t="s">
@@ -69012,7 +69007,7 @@
       <c r="C95" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="D95" s="45" t="s">
+      <c r="D95" s="42" t="s">
         <v>305</v>
       </c>
       <c r="E95" t="s">
@@ -69058,7 +69053,7 @@
       <c r="C96" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D96" s="45" t="s">
+      <c r="D96" s="42" t="s">
         <v>308</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -69103,7 +69098,7 @@
       <c r="C97" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="D97" s="45" t="s">
+      <c r="D97" s="42" t="s">
         <v>311</v>
       </c>
       <c r="E97" t="s">
@@ -69151,7 +69146,7 @@
       <c r="C98" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D98" s="45" t="s">
+      <c r="D98" s="42" t="s">
         <v>54</v>
       </c>
       <c r="E98" t="s">
@@ -69197,7 +69192,7 @@
       <c r="C99" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="D99" s="45" t="s">
+      <c r="D99" s="42" t="s">
         <v>316</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -69242,7 +69237,7 @@
       <c r="C100" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="D100" s="45" t="s">
+      <c r="D100" s="42" t="s">
         <v>320</v>
       </c>
       <c r="E100" t="s">
@@ -69287,7 +69282,7 @@
       <c r="C101" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D101" s="45">
+      <c r="D101" s="42">
         <v>840414684973</v>
       </c>
       <c r="E101" t="s">
@@ -69332,7 +69327,7 @@
       <c r="C102" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D102" s="45" t="s">
+      <c r="D102" s="42" t="s">
         <v>326</v>
       </c>
       <c r="E102" t="s">
@@ -69380,7 +69375,7 @@
       <c r="C103" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D103" s="45" t="s">
+      <c r="D103" s="42" t="s">
         <v>329</v>
       </c>
       <c r="E103" t="s">
@@ -69425,7 +69420,7 @@
       <c r="C104" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D104" s="45" t="s">
+      <c r="D104" s="42" t="s">
         <v>170</v>
       </c>
       <c r="E104" t="s">
@@ -69473,7 +69468,7 @@
       <c r="C105" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D105" s="45" t="s">
+      <c r="D105" s="42" t="s">
         <v>170</v>
       </c>
       <c r="E105" t="s">
@@ -69518,7 +69513,7 @@
       <c r="C106" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D106" s="45" t="s">
+      <c r="D106" s="42" t="s">
         <v>334</v>
       </c>
       <c r="E106" t="s">
@@ -69563,7 +69558,7 @@
       <c r="C107" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D107" s="45" t="s">
+      <c r="D107" s="42" t="s">
         <v>337</v>
       </c>
       <c r="E107" t="s">
@@ -69609,7 +69604,7 @@
       <c r="C108" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D108" s="45" t="s">
+      <c r="D108" s="42" t="s">
         <v>340</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -69654,7 +69649,7 @@
       <c r="C109" s="1">
         <v>4550391046515</v>
       </c>
-      <c r="D109" s="45" t="s">
+      <c r="D109" s="42" t="s">
         <v>342</v>
       </c>
       <c r="E109">
@@ -69699,7 +69694,7 @@
       <c r="C110" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D110" s="45" t="s">
+      <c r="D110" s="42" t="s">
         <v>345</v>
       </c>
       <c r="E110" t="s">
@@ -69744,7 +69739,7 @@
       <c r="C111" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D111" s="45" t="s">
+      <c r="D111" s="42" t="s">
         <v>348</v>
       </c>
       <c r="E111" t="s">
@@ -69790,7 +69785,7 @@
       <c r="C112" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D112" s="45" t="s">
+      <c r="D112" s="42" t="s">
         <v>352</v>
       </c>
       <c r="E112" s="1" t="s">
@@ -69835,7 +69830,7 @@
       <c r="C113" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="D113" s="45" t="s">
+      <c r="D113" s="42" t="s">
         <v>356</v>
       </c>
       <c r="E113" t="s">
@@ -69880,7 +69875,7 @@
       <c r="C114" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D114" s="45" t="s">
+      <c r="D114" s="42" t="s">
         <v>359</v>
       </c>
       <c r="E114" t="s">
@@ -69925,7 +69920,7 @@
       <c r="C115" s="1">
         <v>8720689024570</v>
       </c>
-      <c r="D115" s="45" t="s">
+      <c r="D115" s="42" t="s">
         <v>361</v>
       </c>
       <c r="E115">
@@ -69973,7 +69968,7 @@
       <c r="C116" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="D116" s="45" t="s">
+      <c r="D116" s="42" t="s">
         <v>364</v>
       </c>
       <c r="E116" t="s">
@@ -70018,7 +70013,7 @@
       <c r="C117" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D117" s="45" t="s">
+      <c r="D117" s="42" t="s">
         <v>368</v>
       </c>
       <c r="E117" t="s">
@@ -70063,7 +70058,7 @@
       <c r="C118" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D118" s="45" t="s">
+      <c r="D118" s="42" t="s">
         <v>371</v>
       </c>
       <c r="E118" t="s">
@@ -70108,7 +70103,7 @@
       <c r="C119" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D119" s="45" t="s">
+      <c r="D119" s="42" t="s">
         <v>374</v>
       </c>
       <c r="E119" t="s">
@@ -70153,7 +70148,7 @@
       <c r="C120" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D120" s="45" t="s">
+      <c r="D120" s="42" t="s">
         <v>377</v>
       </c>
       <c r="E120" t="s">
@@ -70199,7 +70194,7 @@
       <c r="C121" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D121" s="45" t="s">
+      <c r="D121" s="42" t="s">
         <v>381</v>
       </c>
       <c r="E121" s="1" t="s">
@@ -70244,7 +70239,7 @@
       <c r="C122" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="D122" s="45" t="s">
+      <c r="D122" s="42" t="s">
         <v>385</v>
       </c>
       <c r="E122" t="s">
@@ -70290,7 +70285,7 @@
       <c r="C123" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D123" s="45" t="s">
+      <c r="D123" s="42" t="s">
         <v>389</v>
       </c>
       <c r="E123" s="1" t="s">
@@ -70335,7 +70330,7 @@
       <c r="C124" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D124" s="45" t="s">
+      <c r="D124" s="42" t="s">
         <v>393</v>
       </c>
       <c r="E124" t="s">
@@ -70383,7 +70378,7 @@
       <c r="C125" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D125" s="45" t="s">
+      <c r="D125" s="42" t="s">
         <v>396</v>
       </c>
       <c r="E125" t="s">
@@ -70431,7 +70426,7 @@
       <c r="C126" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D126" s="45" t="s">
+      <c r="D126" s="42" t="s">
         <v>202</v>
       </c>
       <c r="E126" t="s">
@@ -70479,7 +70474,7 @@
       <c r="C127" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D127" s="45">
+      <c r="D127" s="42">
         <v>4980</v>
       </c>
       <c r="E127" t="s">
@@ -70524,7 +70519,7 @@
       <c r="C128" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D128" s="44" t="s">
+      <c r="D128" s="41" t="s">
         <v>405</v>
       </c>
       <c r="E128" t="s">
@@ -70572,7 +70567,7 @@
       <c r="C129" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="D129" s="45" t="s">
+      <c r="D129" s="42" t="s">
         <v>409</v>
       </c>
       <c r="E129" s="1" t="s">
@@ -70617,7 +70612,7 @@
       <c r="C130" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D130" s="45" t="s">
+      <c r="D130" s="42" t="s">
         <v>413</v>
       </c>
       <c r="E130" t="s">
@@ -70662,7 +70657,7 @@
       <c r="C131" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="D131" s="45" t="s">
+      <c r="D131" s="42" t="s">
         <v>416</v>
       </c>
       <c r="E131" t="s">
@@ -70710,7 +70705,7 @@
       <c r="C132" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D132" s="45" t="s">
+      <c r="D132" s="42" t="s">
         <v>420</v>
       </c>
       <c r="E132" t="s">
@@ -70755,7 +70750,7 @@
       <c r="C133" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D133" s="45" t="s">
+      <c r="D133" s="42" t="s">
         <v>424</v>
       </c>
       <c r="E133" t="s">
@@ -70800,7 +70795,7 @@
       <c r="C134" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D134" s="45" t="s">
+      <c r="D134" s="42" t="s">
         <v>427</v>
       </c>
       <c r="E134" t="s">
@@ -70845,7 +70840,7 @@
       <c r="C135" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D135" s="45" t="s">
+      <c r="D135" s="42" t="s">
         <v>430</v>
       </c>
       <c r="E135" t="s">
@@ -70890,7 +70885,7 @@
       <c r="C136" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D136" s="45" t="s">
+      <c r="D136" s="42" t="s">
         <v>433</v>
       </c>
       <c r="E136" t="s">
@@ -70936,7 +70931,7 @@
       <c r="C137" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D137" s="45" t="s">
+      <c r="D137" s="42" t="s">
         <v>436</v>
       </c>
       <c r="E137" s="1" t="s">
@@ -70981,7 +70976,7 @@
       <c r="C138" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="D138" s="45" t="s">
+      <c r="D138" s="42" t="s">
         <v>439</v>
       </c>
       <c r="E138" t="s">
@@ -71026,7 +71021,7 @@
       <c r="C139" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D139" s="45" t="s">
+      <c r="D139" s="42" t="s">
         <v>442</v>
       </c>
       <c r="E139" t="s">
@@ -71072,7 +71067,7 @@
       <c r="C140" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D140" s="45" t="s">
+      <c r="D140" s="42" t="s">
         <v>446</v>
       </c>
       <c r="E140" s="1" t="s">
@@ -71118,7 +71113,7 @@
       <c r="C141" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D141" s="45" t="s">
+      <c r="D141" s="42" t="s">
         <v>449</v>
       </c>
       <c r="E141" s="1" t="s">
@@ -71163,7 +71158,7 @@
       <c r="C142" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D142" s="45" t="s">
+      <c r="D142" s="42" t="s">
         <v>453</v>
       </c>
       <c r="E142" t="s">
@@ -71211,7 +71206,7 @@
       <c r="C143" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D143" s="45">
+      <c r="D143" s="42">
         <v>4906456568056</v>
       </c>
       <c r="E143" t="s">
@@ -71256,7 +71251,7 @@
       <c r="C144" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="D144" s="45" t="s">
+      <c r="D144" s="42" t="s">
         <v>460</v>
       </c>
       <c r="E144" t="s">
@@ -71301,7 +71296,7 @@
       <c r="C145" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="D145" s="45" t="s">
+      <c r="D145" s="42" t="s">
         <v>463</v>
       </c>
       <c r="E145" t="s">
@@ -71346,7 +71341,7 @@
       <c r="C146" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="D146" s="45" t="s">
+      <c r="D146" s="42" t="s">
         <v>466</v>
       </c>
       <c r="E146" t="s">
@@ -71391,7 +71386,7 @@
       <c r="C147" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="D147" s="45" t="s">
+      <c r="D147" s="42" t="s">
         <v>470</v>
       </c>
       <c r="E147" t="s">
@@ -71439,7 +71434,7 @@
       <c r="C148" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D148" s="45" t="s">
+      <c r="D148" s="42" t="s">
         <v>474</v>
       </c>
       <c r="E148" s="1" t="s">
@@ -71484,7 +71479,7 @@
       <c r="C149" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D149" s="45" t="s">
+      <c r="D149" s="42" t="s">
         <v>478</v>
       </c>
       <c r="E149" t="s">
@@ -71529,7 +71524,7 @@
       <c r="C150" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="D150" s="45" t="s">
+      <c r="D150" s="42" t="s">
         <v>481</v>
       </c>
       <c r="E150" t="s">
@@ -71574,7 +71569,7 @@
       <c r="C151" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="D151" s="45" t="s">
+      <c r="D151" s="42" t="s">
         <v>484</v>
       </c>
       <c r="E151" t="s">
@@ -71619,7 +71614,7 @@
       <c r="C152" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D152" s="45" t="s">
+      <c r="D152" s="42" t="s">
         <v>487</v>
       </c>
       <c r="E152" t="s">
@@ -71664,7 +71659,7 @@
       <c r="C153" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="D153" s="45" t="s">
+      <c r="D153" s="42" t="s">
         <v>490</v>
       </c>
       <c r="E153" t="s">
@@ -71709,7 +71704,7 @@
       <c r="C154" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D154" s="45" t="s">
+      <c r="D154" s="42" t="s">
         <v>493</v>
       </c>
       <c r="E154" t="s">
@@ -71754,7 +71749,7 @@
       <c r="C155" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D155" s="45" t="s">
+      <c r="D155" s="42" t="s">
         <v>497</v>
       </c>
       <c r="E155" t="s">
@@ -71799,7 +71794,7 @@
       <c r="C156" s="1">
         <v>4901416183737</v>
       </c>
-      <c r="D156" s="45" t="s">
+      <c r="D156" s="42" t="s">
         <v>499</v>
       </c>
       <c r="E156">
@@ -71844,7 +71839,7 @@
       <c r="C157" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D157" s="45" t="s">
+      <c r="D157" s="42" t="s">
         <v>502</v>
       </c>
       <c r="E157" t="s">
@@ -71889,7 +71884,7 @@
       <c r="C158" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="D158" s="45" t="s">
+      <c r="D158" s="42" t="s">
         <v>505</v>
       </c>
       <c r="E158" t="s">
@@ -71934,7 +71929,7 @@
       <c r="C159" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="D159" s="45" t="s">
+      <c r="D159" s="42" t="s">
         <v>509</v>
       </c>
       <c r="E159" t="s">
@@ -71982,7 +71977,7 @@
       <c r="C160" s="1">
         <v>4550391046508</v>
       </c>
-      <c r="D160" s="45" t="s">
+      <c r="D160" s="42" t="s">
         <v>512</v>
       </c>
       <c r="E160" t="s">
@@ -72030,7 +72025,7 @@
       <c r="C161" s="1">
         <v>4550391046508</v>
       </c>
-      <c r="D161" s="45" t="s">
+      <c r="D161" s="42" t="s">
         <v>512</v>
       </c>
       <c r="E161" t="s">
@@ -72078,7 +72073,7 @@
       <c r="C162" s="1">
         <v>4550391046508</v>
       </c>
-      <c r="D162" s="45" t="s">
+      <c r="D162" s="42" t="s">
         <v>512</v>
       </c>
       <c r="E162" t="s">
@@ -72124,7 +72119,7 @@
       <c r="C163" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D163" s="45" t="s">
+      <c r="D163" s="42" t="s">
         <v>520</v>
       </c>
       <c r="E163" s="1" t="s">
@@ -72170,7 +72165,7 @@
       <c r="C164" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="D164" s="45" t="s">
+      <c r="D164" s="42" t="s">
         <v>523</v>
       </c>
       <c r="E164" s="1" t="s">
@@ -72215,7 +72210,7 @@
       <c r="C165" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D165" s="45" t="s">
+      <c r="D165" s="42" t="s">
         <v>526</v>
       </c>
       <c r="E165" t="s">
@@ -72260,7 +72255,7 @@
       <c r="C166" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="D166" s="45" t="s">
+      <c r="D166" s="42" t="s">
         <v>530</v>
       </c>
       <c r="E166" t="s">
@@ -72305,7 +72300,7 @@
       <c r="C167" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D167" s="45" t="s">
+      <c r="D167" s="42" t="s">
         <v>533</v>
       </c>
       <c r="E167" t="s">
@@ -72351,7 +72346,7 @@
       <c r="C168" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="D168" s="45" t="s">
+      <c r="D168" s="42" t="s">
         <v>536</v>
       </c>
       <c r="E168" s="1" t="s">
@@ -72396,7 +72391,7 @@
       <c r="C169" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D169" s="45" t="s">
+      <c r="D169" s="42" t="s">
         <v>540</v>
       </c>
       <c r="E169" t="s">
@@ -72441,7 +72436,7 @@
       <c r="C170" s="1">
         <v>4902806133806</v>
       </c>
-      <c r="D170" s="45" t="s">
+      <c r="D170" s="42" t="s">
         <v>542</v>
       </c>
       <c r="E170">
@@ -72489,7 +72484,7 @@
       <c r="C171" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D171" s="45" t="s">
+      <c r="D171" s="42" t="s">
         <v>546</v>
       </c>
       <c r="E171" t="s">
@@ -72534,7 +72529,7 @@
       <c r="C172" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D172" s="45" t="s">
+      <c r="D172" s="42" t="s">
         <v>550</v>
       </c>
       <c r="E172" t="s">
@@ -72579,7 +72574,7 @@
       <c r="C173" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="D173" s="45">
+      <c r="D173" s="42">
         <v>4987176305657</v>
       </c>
       <c r="E173" t="s">
@@ -72624,7 +72619,7 @@
       <c r="C174" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="D174" s="45" t="s">
+      <c r="D174" s="42" t="s">
         <v>555</v>
       </c>
       <c r="E174" t="s">
@@ -72670,7 +72665,7 @@
       <c r="C175" s="1">
         <v>3264680009808</v>
       </c>
-      <c r="D175" s="45" t="s">
+      <c r="D175" s="42" t="s">
         <v>557</v>
       </c>
       <c r="E175" s="1">
@@ -72715,7 +72710,7 @@
       <c r="C176" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="D176" s="45" t="s">
+      <c r="D176" s="42" t="s">
         <v>560</v>
       </c>
       <c r="E176" t="s">
@@ -72761,7 +72756,7 @@
       <c r="C177" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="D177" s="45" t="s">
+      <c r="D177" s="42" t="s">
         <v>564</v>
       </c>
       <c r="E177" s="1" t="s">
@@ -72806,7 +72801,7 @@
       <c r="C178" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="D178" s="45" t="s">
+      <c r="D178" s="42" t="s">
         <v>568</v>
       </c>
       <c r="E178" t="s">
@@ -72851,7 +72846,7 @@
       <c r="C179" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="D179" s="45" t="s">
+      <c r="D179" s="42" t="s">
         <v>571</v>
       </c>
       <c r="E179" t="s">
@@ -72896,7 +72891,7 @@
       <c r="C180" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="D180" s="45" t="s">
+      <c r="D180" s="42" t="s">
         <v>574</v>
       </c>
       <c r="E180" t="s">
@@ -72941,7 +72936,7 @@
       <c r="C181" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="D181" s="45" t="s">
+      <c r="D181" s="42" t="s">
         <v>578</v>
       </c>
       <c r="E181" t="s">
@@ -72987,7 +72982,7 @@
       <c r="C182" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="D182" s="45" t="s">
+      <c r="D182" s="42" t="s">
         <v>581</v>
       </c>
       <c r="E182" s="1" t="s">
@@ -73032,7 +73027,7 @@
       <c r="C183" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="D183" s="45" t="s">
+      <c r="D183" s="42" t="s">
         <v>585</v>
       </c>
       <c r="E183" t="s">
@@ -73077,7 +73072,7 @@
       <c r="C184" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="D184" s="45" t="s">
+      <c r="D184" s="42" t="s">
         <v>588</v>
       </c>
       <c r="E184" t="s">
@@ -73125,7 +73120,7 @@
       <c r="C185" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="D185" s="45" t="s">
+      <c r="D185" s="42" t="s">
         <v>592</v>
       </c>
       <c r="E185" s="1" t="s">
@@ -73170,7 +73165,7 @@
       <c r="C186" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="D186" s="45" t="s">
+      <c r="D186" s="42" t="s">
         <v>596</v>
       </c>
       <c r="E186" t="s">
@@ -73215,7 +73210,7 @@
       <c r="C187" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="D187" s="45" t="s">
+      <c r="D187" s="42" t="s">
         <v>600</v>
       </c>
       <c r="E187" t="s">
@@ -73261,7 +73256,7 @@
       <c r="C188" s="1">
         <v>4902508103596</v>
       </c>
-      <c r="D188" s="45" t="s">
+      <c r="D188" s="42" t="s">
         <v>602</v>
       </c>
       <c r="E188" s="1">
@@ -73306,7 +73301,7 @@
       <c r="C189" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="D189" s="45" t="s">
+      <c r="D189" s="42" t="s">
         <v>605</v>
       </c>
       <c r="E189" t="s">
@@ -73352,7 +73347,7 @@
       <c r="C190" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="D190" s="45" t="s">
+      <c r="D190" s="42" t="s">
         <v>608</v>
       </c>
       <c r="E190" s="1" t="s">
@@ -73397,7 +73392,7 @@
       <c r="C191" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="D191" s="45" t="s">
+      <c r="D191" s="42" t="s">
         <v>611</v>
       </c>
       <c r="E191" t="s">
@@ -73442,7 +73437,7 @@
       <c r="C192" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="D192" s="45" t="s">
+      <c r="D192" s="42" t="s">
         <v>614</v>
       </c>
       <c r="E192" t="s">
@@ -73487,7 +73482,7 @@
       <c r="C193" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="D193" s="45" t="s">
+      <c r="D193" s="42" t="s">
         <v>617</v>
       </c>
       <c r="E193" t="s">
@@ -73532,7 +73527,7 @@
       <c r="C194" s="1" t="s">
         <v>619</v>
       </c>
-      <c r="D194" s="45" t="s">
+      <c r="D194" s="42" t="s">
         <v>620</v>
       </c>
       <c r="E194" t="s">
@@ -73577,7 +73572,7 @@
       <c r="C195" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="D195" s="45" t="s">
+      <c r="D195" s="42" t="s">
         <v>624</v>
       </c>
       <c r="E195" t="s">
@@ -73622,7 +73617,7 @@
       <c r="C196" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="D196" s="45" t="s">
+      <c r="D196" s="42" t="s">
         <v>627</v>
       </c>
       <c r="E196" t="s">
@@ -73670,7 +73665,7 @@
       <c r="C197" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D197" s="45" t="s">
+      <c r="D197" s="42" t="s">
         <v>396</v>
       </c>
       <c r="E197" t="s">
@@ -73715,7 +73710,7 @@
       <c r="C198" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="D198" s="45">
+      <c r="D198" s="42">
         <v>4382</v>
       </c>
       <c r="E198" t="s">
@@ -73761,7 +73756,7 @@
       <c r="C199" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="D199" s="45" t="s">
+      <c r="D199" s="42" t="s">
         <v>634</v>
       </c>
       <c r="E199" s="1" t="s">
@@ -73809,7 +73804,7 @@
       <c r="C200" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D200" s="45" t="s">
+      <c r="D200" s="42" t="s">
         <v>639</v>
       </c>
       <c r="E200" s="1" t="s">
@@ -73857,7 +73852,7 @@
       <c r="C201" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="D201" s="45" t="s">
+      <c r="D201" s="42" t="s">
         <v>546</v>
       </c>
       <c r="E201" t="s">
@@ -73903,7 +73898,7 @@
       <c r="C202" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D202" s="45" t="s">
+      <c r="D202" s="42" t="s">
         <v>645</v>
       </c>
       <c r="E202" s="1" t="s">
@@ -73948,7 +73943,7 @@
       <c r="C203" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="D203" s="45" t="s">
+      <c r="D203" s="42" t="s">
         <v>648</v>
       </c>
       <c r="E203" t="s">
@@ -73993,7 +73988,7 @@
       <c r="C204" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="D204" s="45" t="s">
+      <c r="D204" s="42" t="s">
         <v>651</v>
       </c>
       <c r="E204" t="s">
@@ -74041,7 +74036,7 @@
       <c r="C205" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="D205" s="45" t="s">
+      <c r="D205" s="42" t="s">
         <v>655</v>
       </c>
       <c r="E205" t="s">
@@ -74086,7 +74081,7 @@
       <c r="C206" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="D206" s="45" t="s">
+      <c r="D206" s="42" t="s">
         <v>659</v>
       </c>
       <c r="E206" t="s">
@@ -74131,7 +74126,7 @@
       <c r="C207" s="1">
         <v>4571509303191</v>
       </c>
-      <c r="D207" s="45" t="s">
+      <c r="D207" s="42" t="s">
         <v>661</v>
       </c>
       <c r="E207">
@@ -74176,7 +74171,7 @@
       <c r="C208" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="D208" s="45" t="s">
+      <c r="D208" s="42" t="s">
         <v>664</v>
       </c>
       <c r="E208" t="s">
@@ -74221,7 +74216,7 @@
       <c r="C209" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D209" s="45" t="s">
+      <c r="D209" s="42" t="s">
         <v>667</v>
       </c>
       <c r="E209" t="s">
@@ -74266,7 +74261,7 @@
       <c r="C210" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="D210" s="45" t="s">
+      <c r="D210" s="42" t="s">
         <v>671</v>
       </c>
       <c r="E210" t="s">
@@ -74311,7 +74306,7 @@
       <c r="C211" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="D211" s="45" t="s">
+      <c r="D211" s="42" t="s">
         <v>674</v>
       </c>
       <c r="E211" t="s">
@@ -74356,7 +74351,7 @@
       <c r="C212" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D212" s="45" t="s">
+      <c r="D212" s="42" t="s">
         <v>678</v>
       </c>
       <c r="E212" t="s">
@@ -74401,7 +74396,7 @@
       <c r="C213" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="D213" s="45" t="s">
+      <c r="D213" s="42" t="s">
         <v>681</v>
       </c>
       <c r="E213" t="s">
@@ -74446,7 +74441,7 @@
       <c r="C214" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="D214" s="45" t="s">
+      <c r="D214" s="42" t="s">
         <v>684</v>
       </c>
       <c r="E214" t="s">
@@ -74491,7 +74486,7 @@
       <c r="C215" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="D215" s="45" t="s">
+      <c r="D215" s="42" t="s">
         <v>687</v>
       </c>
       <c r="E215" t="s">
@@ -74536,7 +74531,7 @@
       <c r="C216" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="D216" s="45" t="s">
+      <c r="D216" s="42" t="s">
         <v>691</v>
       </c>
       <c r="E216" t="s">
@@ -74581,7 +74576,7 @@
       <c r="C217" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="D217" s="45" t="s">
+      <c r="D217" s="42" t="s">
         <v>694</v>
       </c>
       <c r="E217" t="s">
@@ -74629,7 +74624,7 @@
       <c r="C218" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D218" s="45" t="s">
+      <c r="D218" s="42" t="s">
         <v>420</v>
       </c>
       <c r="E218" t="s">
@@ -74674,7 +74669,7 @@
       <c r="C219" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="D219" s="45" t="s">
+      <c r="D219" s="42" t="s">
         <v>699</v>
       </c>
       <c r="E219" t="s">
@@ -74720,7 +74715,7 @@
       <c r="C220" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="D220" s="45" t="s">
+      <c r="D220" s="42" t="s">
         <v>702</v>
       </c>
       <c r="E220" s="1" t="s">
@@ -74765,7 +74760,7 @@
       <c r="C221" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="D221" s="45" t="s">
+      <c r="D221" s="42" t="s">
         <v>705</v>
       </c>
       <c r="E221" t="s">
@@ -74810,7 +74805,7 @@
       <c r="C222" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="D222" s="45" t="s">
+      <c r="D222" s="42" t="s">
         <v>709</v>
       </c>
       <c r="E222" t="s">
@@ -74858,7 +74853,7 @@
       <c r="C223" s="1">
         <v>4550391062164</v>
       </c>
-      <c r="D223" s="45" t="s">
+      <c r="D223" s="42" t="s">
         <v>712</v>
       </c>
       <c r="E223">
@@ -74903,7 +74898,7 @@
       <c r="C224" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="D224" s="45">
+      <c r="D224" s="42">
         <v>616</v>
       </c>
       <c r="E224" t="s">
@@ -74951,7 +74946,7 @@
       <c r="C225" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D225" s="45" t="s">
+      <c r="D225" s="42" t="s">
         <v>420</v>
       </c>
       <c r="E225" t="s">
@@ -74997,7 +74992,7 @@
       <c r="C226" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="D226" s="45" t="s">
+      <c r="D226" s="42" t="s">
         <v>719</v>
       </c>
       <c r="E226" s="1" t="s">
@@ -75045,7 +75040,7 @@
       <c r="C227" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D227" s="45" t="s">
+      <c r="D227" s="42" t="s">
         <v>723</v>
       </c>
       <c r="E227" t="s">
@@ -75093,7 +75088,7 @@
       <c r="C228" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D228" s="45" t="s">
+      <c r="D228" s="42" t="s">
         <v>728</v>
       </c>
       <c r="E228" t="s">
@@ -75138,7 +75133,7 @@
       <c r="C229" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="D229" s="45" t="s">
+      <c r="D229" s="42" t="s">
         <v>732</v>
       </c>
       <c r="E229" t="s">
@@ -75184,7 +75179,7 @@
       <c r="C230" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D230" s="45" t="s">
+      <c r="D230" s="42" t="s">
         <v>735</v>
       </c>
       <c r="E230" s="1" t="s">
@@ -75229,7 +75224,7 @@
       <c r="C231" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="D231" s="45" t="s">
+      <c r="D231" s="42" t="s">
         <v>738</v>
       </c>
       <c r="E231" t="s">
@@ -75274,7 +75269,7 @@
       <c r="C232" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="D232" s="45" t="s">
+      <c r="D232" s="42" t="s">
         <v>742</v>
       </c>
       <c r="E232" t="s">
@@ -75319,7 +75314,7 @@
       <c r="C233" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D233" s="45" t="s">
+      <c r="D233" s="42" t="s">
         <v>745</v>
       </c>
       <c r="E233" t="s">
@@ -75364,7 +75359,7 @@
       <c r="C234" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="D234" s="45" t="s">
+      <c r="D234" s="42" t="s">
         <v>748</v>
       </c>
       <c r="E234" t="s">
@@ -75410,7 +75405,7 @@
       <c r="C235" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="D235" s="45" t="s">
+      <c r="D235" s="42" t="s">
         <v>751</v>
       </c>
       <c r="E235" s="1" t="s">
@@ -75455,7 +75450,7 @@
       <c r="C236" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="D236" s="45" t="s">
+      <c r="D236" s="42" t="s">
         <v>754</v>
       </c>
       <c r="E236" t="s">
@@ -75500,7 +75495,7 @@
       <c r="C237" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="D237" s="45" t="s">
+      <c r="D237" s="42" t="s">
         <v>758</v>
       </c>
       <c r="E237" t="s">
@@ -75545,7 +75540,7 @@
       <c r="C238" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="D238" s="45" t="s">
+      <c r="D238" s="42" t="s">
         <v>761</v>
       </c>
       <c r="E238" t="s">
@@ -75590,7 +75585,7 @@
       <c r="C239" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="D239" s="45">
+      <c r="D239" s="42">
         <v>5060144645562</v>
       </c>
       <c r="E239" t="s">
@@ -75638,7 +75633,7 @@
       <c r="C240" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="D240" s="45" t="s">
+      <c r="D240" s="42" t="s">
         <v>768</v>
       </c>
       <c r="E240" t="s">
@@ -75683,7 +75678,7 @@
       <c r="C241" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="D241" s="45" t="s">
+      <c r="D241" s="42" t="s">
         <v>772</v>
       </c>
       <c r="E241" t="s">
@@ -75728,7 +75723,7 @@
       <c r="C242" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="D242" s="45" t="s">
+      <c r="D242" s="42" t="s">
         <v>776</v>
       </c>
       <c r="E242" t="s">
@@ -75773,7 +75768,7 @@
       <c r="C243" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="D243" s="45" t="s">
+      <c r="D243" s="42" t="s">
         <v>780</v>
       </c>
       <c r="E243" t="s">
@@ -75818,7 +75813,7 @@
       <c r="C244" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="D244" s="45" t="s">
+      <c r="D244" s="42" t="s">
         <v>784</v>
       </c>
       <c r="E244" t="s">
@@ -75863,7 +75858,7 @@
       <c r="C245" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="D245" s="45" t="s">
+      <c r="D245" s="42" t="s">
         <v>787</v>
       </c>
       <c r="E245" t="s">
@@ -75908,7 +75903,7 @@
       <c r="C246" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="D246" s="45" t="s">
+      <c r="D246" s="42" t="s">
         <v>790</v>
       </c>
       <c r="E246" t="s">
@@ -75953,7 +75948,7 @@
       <c r="C247" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="D247" s="45" t="s">
+      <c r="D247" s="42" t="s">
         <v>793</v>
       </c>
       <c r="E247" t="s">
@@ -75998,7 +75993,7 @@
       <c r="C248" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="D248" s="45" t="s">
+      <c r="D248" s="42" t="s">
         <v>797</v>
       </c>
       <c r="E248" t="s">
@@ -76037,13 +76032,13 @@
       </c>
     </row>
     <row r="249" spans="1:15" ht="17" customHeight="1">
-      <c r="A249" s="46" t="s">
+      <c r="A249" s="43" t="s">
         <v>799</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="D249" s="45" t="s">
+      <c r="D249" s="42" t="s">
         <v>801</v>
       </c>
       <c r="E249" t="s">
@@ -76088,7 +76083,7 @@
       <c r="C250" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="D250" s="45" t="s">
+      <c r="D250" s="42" t="s">
         <v>804</v>
       </c>
       <c r="E250" t="s">
@@ -76133,7 +76128,7 @@
       <c r="C251" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D251" s="45" t="s">
+      <c r="D251" s="42" t="s">
         <v>807</v>
       </c>
       <c r="E251" t="s">
@@ -76181,7 +76176,7 @@
       <c r="C252" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D252" s="45" t="s">
+      <c r="D252" s="42" t="s">
         <v>728</v>
       </c>
       <c r="E252" t="s">
@@ -76227,7 +76222,7 @@
       <c r="C253" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D253" s="45" t="s">
+      <c r="D253" s="42" t="s">
         <v>812</v>
       </c>
       <c r="E253" s="1" t="s">
@@ -76272,7 +76267,7 @@
       <c r="C254" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="D254" s="45" t="s">
+      <c r="D254" s="42" t="s">
         <v>815</v>
       </c>
       <c r="E254" t="s">
@@ -76317,7 +76312,7 @@
       <c r="C255" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="D255" s="45">
+      <c r="D255" s="42">
         <v>4987176301543</v>
       </c>
       <c r="E255" t="s">
@@ -76362,7 +76357,7 @@
       <c r="C256" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="D256" s="45" t="s">
+      <c r="D256" s="42" t="s">
         <v>820</v>
       </c>
       <c r="E256" t="s">
@@ -76407,7 +76402,7 @@
       <c r="C257" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="D257" s="45" t="s">
+      <c r="D257" s="42" t="s">
         <v>823</v>
       </c>
       <c r="E257" t="s">
@@ -76452,7 +76447,7 @@
       <c r="C258" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="D258" s="45" t="s">
+      <c r="D258" s="42" t="s">
         <v>827</v>
       </c>
       <c r="E258" t="s">
@@ -76497,7 +76492,7 @@
       <c r="C259" s="1">
         <v>4550391012053</v>
       </c>
-      <c r="D259" s="45" t="s">
+      <c r="D259" s="42" t="s">
         <v>829</v>
       </c>
       <c r="E259">
@@ -76542,7 +76537,7 @@
       <c r="C260" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="D260" s="45" t="s">
+      <c r="D260" s="42" t="s">
         <v>832</v>
       </c>
       <c r="E260" t="s">
@@ -76587,7 +76582,7 @@
       <c r="C261" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="D261" s="45" t="s">
+      <c r="D261" s="42" t="s">
         <v>836</v>
       </c>
       <c r="E261" t="s">
@@ -76632,7 +76627,7 @@
       <c r="C262" s="1">
         <v>4550391011926</v>
       </c>
-      <c r="D262" s="45" t="s">
+      <c r="D262" s="42" t="s">
         <v>838</v>
       </c>
       <c r="E262">
@@ -76677,7 +76672,7 @@
       <c r="C263" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="D263" s="45" t="s">
+      <c r="D263" s="42" t="s">
         <v>841</v>
       </c>
       <c r="E263" t="s">
@@ -76722,7 +76717,7 @@
       <c r="C264" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="D264" s="45" t="s">
+      <c r="D264" s="42" t="s">
         <v>844</v>
       </c>
       <c r="E264" t="s">
@@ -76767,7 +76762,7 @@
       <c r="C265" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D265" s="45" t="s">
+      <c r="D265" s="42" t="s">
         <v>847</v>
       </c>
       <c r="E265" t="s">
@@ -76812,7 +76807,7 @@
       <c r="C266" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="D266" s="45" t="s">
+      <c r="D266" s="42" t="s">
         <v>850</v>
       </c>
       <c r="E266" t="s">
@@ -76857,7 +76852,7 @@
       <c r="C267" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="D267" s="45" t="s">
+      <c r="D267" s="42" t="s">
         <v>853</v>
       </c>
       <c r="E267" t="s">
@@ -76902,7 +76897,7 @@
       <c r="C268" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="D268" s="45" t="s">
+      <c r="D268" s="42" t="s">
         <v>856</v>
       </c>
       <c r="E268" t="s">
@@ -76947,7 +76942,7 @@
       <c r="C269" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="D269" s="45" t="s">
+      <c r="D269" s="42" t="s">
         <v>859</v>
       </c>
       <c r="E269" t="s">
@@ -76995,7 +76990,7 @@
       <c r="C270" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="D270" s="45" t="s">
+      <c r="D270" s="42" t="s">
         <v>863</v>
       </c>
       <c r="E270" t="s">
@@ -77040,7 +77035,7 @@
       <c r="C271" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D271" s="45" t="s">
+      <c r="D271" s="42" t="s">
         <v>867</v>
       </c>
       <c r="E271" t="s">
@@ -77085,7 +77080,7 @@
       <c r="C272" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="D272" s="45" t="s">
+      <c r="D272" s="42" t="s">
         <v>870</v>
       </c>
       <c r="E272" t="s">
@@ -77133,7 +77128,7 @@
       <c r="C273" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="D273" s="45" t="s">
+      <c r="D273" s="42" t="s">
         <v>874</v>
       </c>
       <c r="E273" t="s">
@@ -77181,7 +77176,7 @@
       <c r="C274" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D274" s="45" t="s">
+      <c r="D274" s="42" t="s">
         <v>639</v>
       </c>
       <c r="E274" t="s">
@@ -77226,7 +77221,7 @@
       <c r="C275" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="D275" s="45" t="s">
+      <c r="D275" s="42" t="s">
         <v>880</v>
       </c>
       <c r="E275" t="s">
@@ -77274,7 +77269,7 @@
       <c r="C276" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D276" s="45" t="s">
+      <c r="D276" s="42" t="s">
         <v>728</v>
       </c>
       <c r="E276" t="s">
@@ -77322,7 +77317,7 @@
       <c r="C277" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D277" s="45" t="s">
+      <c r="D277" s="42" t="s">
         <v>639</v>
       </c>
       <c r="E277" t="s">
@@ -77370,7 +77365,7 @@
       <c r="C278" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="D278" s="45" t="s">
+      <c r="D278" s="42" t="s">
         <v>639</v>
       </c>
       <c r="E278" s="1" t="s">
@@ -77415,7 +77410,7 @@
       <c r="C279" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="D279" s="45" t="s">
+      <c r="D279" s="42" t="s">
         <v>889</v>
       </c>
       <c r="E279" t="s">
@@ -77460,7 +77455,7 @@
       <c r="C280" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="D280" s="45" t="s">
+      <c r="D280" s="42" t="s">
         <v>893</v>
       </c>
       <c r="E280" t="s">
@@ -77505,7 +77500,7 @@
       <c r="C281" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="D281" s="45" t="s">
+      <c r="D281" s="42" t="s">
         <v>896</v>
       </c>
       <c r="E281" t="s">
@@ -77550,7 +77545,7 @@
       <c r="C282" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="D282" s="45" t="s">
+      <c r="D282" s="42" t="s">
         <v>493</v>
       </c>
       <c r="E282" t="s">
@@ -77595,7 +77590,7 @@
       <c r="C283" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="D283" s="45">
+      <c r="D283" s="42">
         <v>720</v>
       </c>
       <c r="E283" t="s">
@@ -77640,7 +77635,7 @@
       <c r="C284" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="D284" s="45" t="s">
+      <c r="D284" s="42" t="s">
         <v>903</v>
       </c>
       <c r="E284" t="s">
@@ -77686,7 +77681,7 @@
       <c r="C285" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="D285" s="45" t="s">
+      <c r="D285" s="42" t="s">
         <v>906</v>
       </c>
       <c r="E285" s="1" t="s">
@@ -77731,7 +77726,7 @@
       <c r="C286" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="D286" s="45" t="s">
+      <c r="D286" s="42" t="s">
         <v>909</v>
       </c>
       <c r="E286" t="s">
@@ -77777,7 +77772,7 @@
       <c r="C287" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="D287" s="45" t="s">
+      <c r="D287" s="42" t="s">
         <v>912</v>
       </c>
       <c r="E287" s="1" t="s">
@@ -77822,7 +77817,7 @@
       <c r="C288" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="D288" s="45" t="s">
+      <c r="D288" s="42" t="s">
         <v>915</v>
       </c>
       <c r="E288" t="s">
@@ -77867,7 +77862,7 @@
       <c r="C289" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="D289" s="45" t="s">
+      <c r="D289" s="42" t="s">
         <v>918</v>
       </c>
       <c r="E289" t="s">
@@ -77913,7 +77908,7 @@
       <c r="C290" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="D290" s="45" t="s">
+      <c r="D290" s="42" t="s">
         <v>922</v>
       </c>
       <c r="E290" s="1" t="s">
@@ -77958,7 +77953,7 @@
       <c r="C291" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="D291" s="45" t="s">
+      <c r="D291" s="42" t="s">
         <v>925</v>
       </c>
       <c r="E291" t="s">
@@ -78004,7 +77999,7 @@
       <c r="C292" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="D292" s="45" t="s">
+      <c r="D292" s="42" t="s">
         <v>929</v>
       </c>
       <c r="E292" s="1" t="s">
@@ -78049,7 +78044,7 @@
       <c r="C293" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="D293" s="45" t="s">
+      <c r="D293" s="42" t="s">
         <v>932</v>
       </c>
       <c r="E293" t="s">
@@ -78095,7 +78090,7 @@
       <c r="C294" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="D294" s="45" t="s">
+      <c r="D294" s="42" t="s">
         <v>936</v>
       </c>
       <c r="E294" s="1" t="s">
@@ -78140,7 +78135,7 @@
       <c r="C295" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="D295" s="45">
+      <c r="D295" s="42">
         <v>199</v>
       </c>
       <c r="E295" t="s">
@@ -78185,7 +78180,7 @@
       <c r="C296" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="D296" s="45" t="s">
+      <c r="D296" s="42" t="s">
         <v>941</v>
       </c>
       <c r="E296" t="s">
@@ -78231,7 +78226,7 @@
       <c r="C297" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="D297" s="45" t="s">
+      <c r="D297" s="42" t="s">
         <v>944</v>
       </c>
       <c r="E297" s="1" t="s">
@@ -78276,7 +78271,7 @@
       <c r="C298" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="D298" s="45" t="s">
+      <c r="D298" s="42" t="s">
         <v>947</v>
       </c>
       <c r="E298" t="s">
@@ -78321,7 +78316,7 @@
       <c r="C299" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="D299" s="45" t="s">
+      <c r="D299" s="42" t="s">
         <v>951</v>
       </c>
       <c r="E299" t="s">
@@ -78366,7 +78361,7 @@
       <c r="C300" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="D300" s="45" t="s">
+      <c r="D300" s="42" t="s">
         <v>954</v>
       </c>
       <c r="E300" t="s">
@@ -78439,7 +78434,7 @@
       <c r="M303" s="30" t="s">
         <v>956</v>
       </c>
-      <c r="N303" s="41">
+      <c r="N303" s="44">
         <v>76791</v>
       </c>
       <c r="O303" s="32">
@@ -78451,7 +78446,7 @@
       <c r="M304" s="33" t="s">
         <v>957</v>
       </c>
-      <c r="N304" s="42">
+      <c r="N304" s="45">
         <v>96798</v>
       </c>
       <c r="O304" s="34">
@@ -78463,7 +78458,7 @@
       <c r="M305" s="33" t="s">
         <v>958</v>
       </c>
-      <c r="N305" s="42">
+      <c r="N305" s="45">
         <v>11700</v>
       </c>
       <c r="O305" s="34">
@@ -78475,7 +78470,7 @@
       <c r="M306" s="33" t="s">
         <v>959</v>
       </c>
-      <c r="N306" s="42">
+      <c r="N306" s="45">
         <v>0</v>
       </c>
       <c r="O306" s="35"/>
@@ -78502,7 +78497,7 @@
       <c r="M309" s="33" t="s">
         <v>961</v>
       </c>
-      <c r="N309" s="42">
+      <c r="N309" s="45">
         <v>248314</v>
       </c>
       <c r="O309" s="34">
@@ -78514,7 +78509,7 @@
       <c r="M310" s="36" t="s">
         <v>962</v>
       </c>
-      <c r="N310" s="43">
+      <c r="N310" s="46">
         <v>36608</v>
       </c>
       <c r="O310" s="34">
